--- a/resources/Marks/2026/even/Physics For Computer Engineers.xlsx
+++ b/resources/Marks/2026/even/Physics For Computer Engineers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gusindia01-my.sharepoint.com/personal/nitesh_kumar_ddn_upes_ac_in/Documents/UPES/2026/Jan-May-2026/Physics for Computer Engineers B77 B78/Marks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3625" documentId="11_3FC952BF37FB7C428065D6D94F732ED04C5A5A3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67D53DCB-FBBB-4F9D-8EBA-FB7C369C7DBE}"/>
+  <xr:revisionPtr revIDLastSave="3578" documentId="11_3FC952BF37FB7C428065D6D94F732ED04C5A5A3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2430891F-A738-483A-AA82-FF0CCB144A0F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="553" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,12 +22,12 @@
     <sheet name="Assignment 1" sheetId="6" r:id="rId7"/>
     <sheet name="Assignment 2" sheetId="9" r:id="rId8"/>
     <sheet name="Class Test 2" sheetId="8" r:id="rId9"/>
-    <sheet name="Lab Marks " sheetId="16" r:id="rId10"/>
+    <sheet name="Remedial Class" sheetId="15" r:id="rId10"/>
     <sheet name="Sheet2" sheetId="11" state="hidden" r:id="rId11"/>
     <sheet name="Sheet3" sheetId="12" state="hidden" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Class Test 2'!$B$5:$C$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Class Test 2'!$A$4:$B$64</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="176">
   <si>
     <t>Final Marks</t>
   </si>
@@ -608,20 +608,20 @@
     <t>CO2/CO1</t>
   </si>
   <si>
+    <t>Remedial Class Attendance (Batch 77/78) Jan-June 2026</t>
+  </si>
+  <si>
     <t>CO5</t>
   </si>
   <si>
-    <t>Median (including 0)</t>
-  </si>
-  <si>
-    <t>Lab Marks</t>
+    <t>SN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -677,6 +677,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -801,7 +808,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -922,6 +929,15 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -931,8 +947,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1533,51 +1549,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="44" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
+      <c r="A1" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
       <c r="T1" s="24"/>
     </row>
     <row r="2" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="47" t="s">
         <v>168</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="44"/>
-      <c r="S2" s="44"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="47"/>
+      <c r="S2" s="47"/>
       <c r="T2" s="25"/>
     </row>
     <row r="3" spans="1:22" s="22" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
@@ -3276,7 +3292,7 @@
       </c>
       <c r="H25" s="10">
         <f>'Assignment 2'!N26</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I25" s="10">
         <f>'Class Test 2'!O26</f>
@@ -3284,18 +3300,18 @@
       </c>
       <c r="J25" s="29">
         <f t="shared" si="0"/>
-        <v>83.8</v>
+        <v>97.8</v>
       </c>
       <c r="K25" s="29">
         <v>93.5</v>
       </c>
       <c r="L25" s="29">
         <f t="shared" si="1"/>
-        <v>88.65</v>
+        <v>95.65</v>
       </c>
       <c r="M25" s="29">
         <f t="shared" si="2"/>
-        <v>44.325000000000003</v>
+        <v>47.825000000000003</v>
       </c>
       <c r="N25" s="29">
         <f t="shared" si="3"/>
@@ -3315,7 +3331,7 @@
       </c>
       <c r="R25" s="26">
         <f t="shared" si="5"/>
-        <v>61.325000000000003</v>
+        <v>64.825000000000003</v>
       </c>
       <c r="S25" s="36"/>
       <c r="U25" t="s">
@@ -3979,14 +3995,16 @@
         <f t="shared" si="0"/>
         <v>82.6</v>
       </c>
-      <c r="K34" s="29"/>
+      <c r="K34" s="29">
+        <v>62.5</v>
+      </c>
       <c r="L34" s="29">
         <f t="shared" si="1"/>
-        <v>41.3</v>
+        <v>72.55</v>
       </c>
       <c r="M34" s="29">
         <f t="shared" si="2"/>
-        <v>20.65</v>
+        <v>36.274999999999999</v>
       </c>
       <c r="N34" s="29">
         <f t="shared" si="3"/>
@@ -4006,7 +4024,7 @@
       </c>
       <c r="R34" s="26">
         <f t="shared" si="5"/>
-        <v>28.25</v>
+        <v>43.875</v>
       </c>
       <c r="S34" s="36"/>
       <c r="U34" t="s">
@@ -4054,14 +4072,16 @@
         <f t="shared" si="0"/>
         <v>88.9</v>
       </c>
-      <c r="K35" s="29"/>
+      <c r="K35" s="29">
+        <v>43.5</v>
+      </c>
       <c r="L35" s="29">
         <f t="shared" si="1"/>
-        <v>44.45</v>
+        <v>66.2</v>
       </c>
       <c r="M35" s="29">
         <f t="shared" si="2"/>
-        <v>22.225000000000001</v>
+        <v>33.1</v>
       </c>
       <c r="N35" s="29">
         <f t="shared" si="3"/>
@@ -4081,7 +4101,7 @@
       </c>
       <c r="R35" s="26">
         <f t="shared" si="5"/>
-        <v>22.225000000000001</v>
+        <v>33.1</v>
       </c>
       <c r="S35" s="36"/>
       <c r="U35" t="s">
@@ -4129,14 +4149,16 @@
         <f t="shared" si="0"/>
         <v>88.9</v>
       </c>
-      <c r="K36" s="29"/>
+      <c r="K36" s="29">
+        <v>68</v>
+      </c>
       <c r="L36" s="29">
         <f t="shared" si="1"/>
-        <v>44.45</v>
+        <v>78.45</v>
       </c>
       <c r="M36" s="29">
         <f t="shared" si="2"/>
-        <v>22.225000000000001</v>
+        <v>39.225000000000001</v>
       </c>
       <c r="N36" s="29">
         <f t="shared" si="3"/>
@@ -4156,7 +4178,7 @@
       </c>
       <c r="R36" s="26">
         <f t="shared" si="5"/>
-        <v>28.425000000000001</v>
+        <v>45.425000000000004</v>
       </c>
       <c r="S36" s="36"/>
       <c r="U36" t="s">
@@ -4204,14 +4226,16 @@
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="K37" s="29"/>
+      <c r="K37" s="29">
+        <v>66.5</v>
+      </c>
       <c r="L37" s="29">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>73.25</v>
       </c>
       <c r="M37" s="29">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>36.625</v>
       </c>
       <c r="N37" s="29">
         <f t="shared" si="3"/>
@@ -4231,7 +4255,7 @@
       </c>
       <c r="R37" s="26">
         <f t="shared" si="5"/>
-        <v>31.2</v>
+        <v>47.825000000000003</v>
       </c>
       <c r="S37" s="36"/>
       <c r="U37" t="s">
@@ -4279,14 +4303,16 @@
         <f t="shared" si="0"/>
         <v>60.9</v>
       </c>
-      <c r="K38" s="29"/>
+      <c r="K38" s="29">
+        <v>40</v>
+      </c>
       <c r="L38" s="29">
         <f t="shared" si="1"/>
-        <v>30.45</v>
+        <v>50.45</v>
       </c>
       <c r="M38" s="29">
         <f t="shared" si="2"/>
-        <v>15.225</v>
+        <v>25.225000000000001</v>
       </c>
       <c r="N38" s="29">
         <f t="shared" si="3"/>
@@ -4306,7 +4332,7 @@
       </c>
       <c r="R38" s="26">
         <f t="shared" si="5"/>
-        <v>15.625</v>
+        <v>25.625</v>
       </c>
       <c r="S38" s="1"/>
       <c r="U38" t="s">
@@ -4354,14 +4380,16 @@
         <f t="shared" si="0"/>
         <v>44.5</v>
       </c>
-      <c r="K39" s="29"/>
+      <c r="K39" s="29">
+        <v>39</v>
+      </c>
       <c r="L39" s="29">
         <f t="shared" si="1"/>
-        <v>22.25</v>
+        <v>41.75</v>
       </c>
       <c r="M39" s="29">
         <f t="shared" si="2"/>
-        <v>11.125</v>
+        <v>20.875</v>
       </c>
       <c r="N39" s="29">
         <f t="shared" si="3"/>
@@ -4381,7 +4409,7 @@
       </c>
       <c r="R39" s="26">
         <f t="shared" si="5"/>
-        <v>21.925000000000001</v>
+        <v>31.675000000000001</v>
       </c>
       <c r="S39" s="1"/>
       <c r="U39" t="s">
@@ -4429,14 +4457,16 @@
         <f t="shared" si="0"/>
         <v>24.5</v>
       </c>
-      <c r="K40" s="29"/>
+      <c r="K40" s="29">
+        <v>39</v>
+      </c>
       <c r="L40" s="29">
         <f t="shared" si="1"/>
-        <v>12.25</v>
+        <v>31.75</v>
       </c>
       <c r="M40" s="29">
         <f t="shared" si="2"/>
-        <v>6.125</v>
+        <v>15.875</v>
       </c>
       <c r="N40" s="29">
         <f t="shared" si="3"/>
@@ -4456,7 +4486,7 @@
       </c>
       <c r="R40" s="26">
         <f t="shared" si="5"/>
-        <v>6.9249999999999998</v>
+        <v>16.675000000000001</v>
       </c>
       <c r="S40" s="1"/>
       <c r="U40" t="s">
@@ -4504,14 +4534,16 @@
         <f t="shared" si="0"/>
         <v>66.099999999999994</v>
       </c>
-      <c r="K41" s="29"/>
+      <c r="K41" s="29">
+        <v>68.5</v>
+      </c>
       <c r="L41" s="29">
         <f t="shared" si="1"/>
-        <v>33.049999999999997</v>
+        <v>67.3</v>
       </c>
       <c r="M41" s="29">
         <f t="shared" si="2"/>
-        <v>16.524999999999999</v>
+        <v>33.65</v>
       </c>
       <c r="N41" s="29">
         <f t="shared" si="3"/>
@@ -4531,7 +4563,7 @@
       </c>
       <c r="R41" s="26">
         <f t="shared" si="5"/>
-        <v>22.524999999999999</v>
+        <v>39.65</v>
       </c>
       <c r="S41" s="1"/>
       <c r="U41" t="s">
@@ -4579,14 +4611,16 @@
         <f t="shared" si="0"/>
         <v>17.5</v>
       </c>
-      <c r="K42" s="29"/>
+      <c r="K42" s="29">
+        <v>16</v>
+      </c>
       <c r="L42" s="29">
         <f t="shared" si="1"/>
-        <v>8.75</v>
+        <v>16.75</v>
       </c>
       <c r="M42" s="29">
         <f t="shared" si="2"/>
-        <v>4.375</v>
+        <v>8.375</v>
       </c>
       <c r="N42" s="29">
         <f t="shared" si="3"/>
@@ -4606,7 +4640,7 @@
       </c>
       <c r="R42" s="26">
         <f t="shared" si="5"/>
-        <v>6.7750000000000004</v>
+        <v>10.775</v>
       </c>
       <c r="S42" s="1"/>
       <c r="U42" t="s">
@@ -4654,7 +4688,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K43" s="29"/>
+      <c r="K43" s="29">
+        <v>0</v>
+      </c>
       <c r="L43" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4729,14 +4765,16 @@
         <f t="shared" si="0"/>
         <v>83.4</v>
       </c>
-      <c r="K44" s="29"/>
+      <c r="K44" s="29">
+        <v>70</v>
+      </c>
       <c r="L44" s="29">
         <f t="shared" si="1"/>
-        <v>41.7</v>
+        <v>76.7</v>
       </c>
       <c r="M44" s="29">
         <f t="shared" si="2"/>
-        <v>20.85</v>
+        <v>38.35</v>
       </c>
       <c r="N44" s="29">
         <f t="shared" si="3"/>
@@ -4756,7 +4794,7 @@
       </c>
       <c r="R44" s="26">
         <f t="shared" si="5"/>
-        <v>23.05</v>
+        <v>40.550000000000004</v>
       </c>
       <c r="S44" s="1"/>
       <c r="U44" t="s">
@@ -4804,14 +4842,16 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="K45" s="29"/>
+      <c r="K45" s="29">
+        <v>5</v>
+      </c>
       <c r="L45" s="29">
         <f t="shared" si="1"/>
-        <v>9.5</v>
+        <v>12</v>
       </c>
       <c r="M45" s="29">
         <f t="shared" si="2"/>
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="N45" s="29">
         <f t="shared" si="3"/>
@@ -4831,7 +4871,7 @@
       </c>
       <c r="R45" s="26">
         <f t="shared" si="5"/>
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="S45" s="1"/>
       <c r="U45" t="s">
@@ -4879,14 +4919,16 @@
         <f t="shared" si="0"/>
         <v>80.8</v>
       </c>
-      <c r="K46" s="29"/>
+      <c r="K46" s="29">
+        <v>48</v>
+      </c>
       <c r="L46" s="29">
         <f t="shared" si="1"/>
-        <v>40.4</v>
+        <v>64.400000000000006</v>
       </c>
       <c r="M46" s="29">
         <f t="shared" si="2"/>
-        <v>20.2</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="N46" s="29">
         <f t="shared" si="3"/>
@@ -4906,7 +4948,7 @@
       </c>
       <c r="R46" s="26">
         <f t="shared" si="5"/>
-        <v>22.2</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="S46" s="1"/>
       <c r="U46" t="s">
@@ -4954,14 +4996,16 @@
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="K47" s="29"/>
+      <c r="K47" s="29">
+        <v>27</v>
+      </c>
       <c r="L47" s="29">
         <f t="shared" si="1"/>
-        <v>21.5</v>
+        <v>35</v>
       </c>
       <c r="M47" s="29">
         <f t="shared" si="2"/>
-        <v>10.75</v>
+        <v>17.5</v>
       </c>
       <c r="N47" s="29">
         <f t="shared" si="3"/>
@@ -4981,7 +5025,7 @@
       </c>
       <c r="R47" s="26">
         <f t="shared" si="5"/>
-        <v>11.55</v>
+        <v>18.3</v>
       </c>
       <c r="S47" s="1"/>
       <c r="U47" t="s">
@@ -5029,14 +5073,16 @@
         <f t="shared" si="0"/>
         <v>70.900000000000006</v>
       </c>
-      <c r="K48" s="29"/>
+      <c r="K48" s="29">
+        <v>53</v>
+      </c>
       <c r="L48" s="29">
         <f t="shared" si="1"/>
-        <v>35.450000000000003</v>
+        <v>61.95</v>
       </c>
       <c r="M48" s="29">
         <f t="shared" si="2"/>
-        <v>17.725000000000001</v>
+        <v>30.975000000000001</v>
       </c>
       <c r="N48" s="29">
         <f t="shared" si="3"/>
@@ -5056,7 +5102,7 @@
       </c>
       <c r="R48" s="26">
         <f t="shared" si="5"/>
-        <v>17.725000000000001</v>
+        <v>30.975000000000001</v>
       </c>
       <c r="S48" s="1"/>
       <c r="U48" t="s">
@@ -5104,7 +5150,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K49" s="29"/>
+      <c r="K49" s="29">
+        <v>0</v>
+      </c>
       <c r="L49" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -5179,14 +5227,16 @@
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="K50" s="29"/>
+      <c r="K50" s="29">
+        <v>70.5</v>
+      </c>
       <c r="L50" s="29">
         <f t="shared" si="1"/>
-        <v>36</v>
+        <v>71.25</v>
       </c>
       <c r="M50" s="29">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>35.625</v>
       </c>
       <c r="N50" s="29">
         <f t="shared" si="3"/>
@@ -5206,7 +5256,7 @@
       </c>
       <c r="R50" s="26">
         <f t="shared" si="5"/>
-        <v>27.2</v>
+        <v>44.825000000000003</v>
       </c>
       <c r="S50" s="1"/>
       <c r="U50" t="s">
@@ -5254,14 +5304,16 @@
         <f t="shared" si="0"/>
         <v>92.9</v>
       </c>
-      <c r="K51" s="29"/>
+      <c r="K51" s="29">
+        <v>40</v>
+      </c>
       <c r="L51" s="29">
         <f t="shared" si="1"/>
-        <v>46.45</v>
+        <v>66.45</v>
       </c>
       <c r="M51" s="29">
         <f t="shared" si="2"/>
-        <v>23.225000000000001</v>
+        <v>33.225000000000001</v>
       </c>
       <c r="N51" s="29">
         <f t="shared" si="3"/>
@@ -5281,7 +5333,7 @@
       </c>
       <c r="R51" s="26">
         <f t="shared" si="5"/>
-        <v>23.425000000000001</v>
+        <v>33.425000000000004</v>
       </c>
       <c r="S51" s="1"/>
       <c r="U51" t="s">
@@ -5329,7 +5381,9 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="K52" s="29"/>
+      <c r="K52" s="29">
+        <v>0</v>
+      </c>
       <c r="L52" s="29">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -5404,14 +5458,16 @@
         <f t="shared" si="0"/>
         <v>70.900000000000006</v>
       </c>
-      <c r="K53" s="1"/>
+      <c r="K53" s="12">
+        <v>46</v>
+      </c>
       <c r="L53" s="29">
         <f t="shared" si="1"/>
-        <v>35.450000000000003</v>
+        <v>58.45</v>
       </c>
       <c r="M53" s="29">
         <f t="shared" si="2"/>
-        <v>17.725000000000001</v>
+        <v>29.225000000000001</v>
       </c>
       <c r="N53" s="29">
         <f t="shared" si="3"/>
@@ -5431,7 +5487,7 @@
       </c>
       <c r="R53" s="26">
         <f t="shared" si="5"/>
-        <v>21.125</v>
+        <v>32.625</v>
       </c>
       <c r="S53" s="1"/>
       <c r="U53" t="s">
@@ -5479,14 +5535,16 @@
         <f t="shared" si="0"/>
         <v>94.6</v>
       </c>
-      <c r="K54" s="1"/>
+      <c r="K54" s="12">
+        <v>52.5</v>
+      </c>
       <c r="L54" s="29">
         <f t="shared" si="1"/>
-        <v>47.3</v>
+        <v>73.55</v>
       </c>
       <c r="M54" s="29">
         <f t="shared" si="2"/>
-        <v>23.65</v>
+        <v>36.774999999999999</v>
       </c>
       <c r="N54" s="29">
         <f t="shared" si="3"/>
@@ -5506,7 +5564,7 @@
       </c>
       <c r="R54" s="26">
         <f t="shared" si="5"/>
-        <v>27.049999999999997</v>
+        <v>40.174999999999997</v>
       </c>
       <c r="S54" s="1"/>
       <c r="U54" t="s">
@@ -5554,14 +5612,16 @@
         <f t="shared" si="0"/>
         <v>64.3</v>
       </c>
-      <c r="K55" s="1"/>
+      <c r="K55" s="12">
+        <v>37</v>
+      </c>
       <c r="L55" s="29">
         <f t="shared" si="1"/>
-        <v>32.15</v>
+        <v>50.65</v>
       </c>
       <c r="M55" s="29">
         <f t="shared" si="2"/>
-        <v>16.074999999999999</v>
+        <v>25.324999999999999</v>
       </c>
       <c r="N55" s="29">
         <f t="shared" si="3"/>
@@ -5581,7 +5641,7 @@
       </c>
       <c r="R55" s="26">
         <f t="shared" si="5"/>
-        <v>16.074999999999999</v>
+        <v>25.324999999999999</v>
       </c>
       <c r="S55" s="1"/>
       <c r="U55" t="s">
@@ -5629,14 +5689,16 @@
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="K56" s="1"/>
+      <c r="K56" s="12">
+        <v>23</v>
+      </c>
       <c r="L56" s="29">
         <f t="shared" si="1"/>
-        <v>23.5</v>
+        <v>35</v>
       </c>
       <c r="M56" s="29">
         <f t="shared" si="2"/>
-        <v>11.75</v>
+        <v>17.5</v>
       </c>
       <c r="N56" s="29">
         <f t="shared" si="3"/>
@@ -5656,7 +5718,7 @@
       </c>
       <c r="R56" s="26">
         <f t="shared" si="5"/>
-        <v>16.149999999999999</v>
+        <v>21.9</v>
       </c>
       <c r="S56" s="1"/>
       <c r="U56" t="s">
@@ -5704,14 +5766,16 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="K57" s="1"/>
+      <c r="K57" s="12">
+        <v>8.5</v>
+      </c>
       <c r="L57" s="29">
         <f t="shared" si="1"/>
-        <v>13.5</v>
+        <v>17.75</v>
       </c>
       <c r="M57" s="29">
         <f t="shared" si="2"/>
-        <v>6.75</v>
+        <v>8.875</v>
       </c>
       <c r="N57" s="29">
         <f t="shared" si="3"/>
@@ -5731,7 +5795,7 @@
       </c>
       <c r="R57" s="26">
         <f t="shared" si="5"/>
-        <v>8.5500000000000007</v>
+        <v>10.675000000000001</v>
       </c>
       <c r="S57" s="1"/>
       <c r="U57" t="s">
@@ -5779,14 +5843,16 @@
         <f t="shared" si="0"/>
         <v>88.8</v>
       </c>
-      <c r="K58" s="1"/>
+      <c r="K58" s="12">
+        <v>80</v>
+      </c>
       <c r="L58" s="29">
         <f t="shared" si="1"/>
-        <v>44.4</v>
+        <v>84.4</v>
       </c>
       <c r="M58" s="29">
         <f t="shared" si="2"/>
-        <v>22.2</v>
+        <v>42.2</v>
       </c>
       <c r="N58" s="29">
         <f t="shared" si="3"/>
@@ -5806,7 +5872,7 @@
       </c>
       <c r="R58" s="26">
         <f t="shared" si="5"/>
-        <v>38.599999999999994</v>
+        <v>58.6</v>
       </c>
       <c r="S58" s="1"/>
       <c r="U58" t="s">
@@ -5854,14 +5920,16 @@
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
-      <c r="K59" s="1"/>
+      <c r="K59" s="12">
+        <v>67</v>
+      </c>
       <c r="L59" s="29">
         <f t="shared" si="1"/>
-        <v>42.5</v>
+        <v>76</v>
       </c>
       <c r="M59" s="29">
         <f t="shared" si="2"/>
-        <v>21.25</v>
+        <v>38</v>
       </c>
       <c r="N59" s="29">
         <f t="shared" si="3"/>
@@ -5881,7 +5949,7 @@
       </c>
       <c r="R59" s="26">
         <f t="shared" si="5"/>
-        <v>27.45</v>
+        <v>44.2</v>
       </c>
       <c r="S59" s="1"/>
       <c r="U59" t="s">
@@ -5929,14 +5997,16 @@
         <f t="shared" si="0"/>
         <v>82.2</v>
       </c>
-      <c r="K60" s="1"/>
+      <c r="K60" s="12">
+        <v>80</v>
+      </c>
       <c r="L60" s="29">
         <f t="shared" si="1"/>
-        <v>41.1</v>
+        <v>81.099999999999994</v>
       </c>
       <c r="M60" s="29">
         <f t="shared" si="2"/>
-        <v>20.55</v>
+        <v>40.549999999999997</v>
       </c>
       <c r="N60" s="29">
         <f t="shared" si="3"/>
@@ -5956,7 +6026,7 @@
       </c>
       <c r="R60" s="26">
         <f t="shared" si="5"/>
-        <v>34.15</v>
+        <v>54.15</v>
       </c>
       <c r="S60" s="1"/>
       <c r="U60" t="s">
@@ -6004,14 +6074,16 @@
         <f t="shared" si="0"/>
         <v>89.7</v>
       </c>
-      <c r="K61" s="1"/>
+      <c r="K61" s="12">
+        <v>51.5</v>
+      </c>
       <c r="L61" s="29">
         <f t="shared" si="1"/>
-        <v>44.85</v>
+        <v>70.599999999999994</v>
       </c>
       <c r="M61" s="29">
         <f t="shared" si="2"/>
-        <v>22.425000000000001</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="N61" s="29">
         <f t="shared" si="3"/>
@@ -6031,7 +6103,7 @@
       </c>
       <c r="R61" s="26">
         <f t="shared" si="5"/>
-        <v>34.424999999999997</v>
+        <v>47.3</v>
       </c>
       <c r="S61" s="1"/>
       <c r="U61" t="s">
@@ -6079,14 +6151,16 @@
         <f t="shared" si="0"/>
         <v>82.5</v>
       </c>
-      <c r="K62" s="1"/>
+      <c r="K62" s="12">
+        <v>51</v>
+      </c>
       <c r="L62" s="29">
         <f t="shared" si="1"/>
-        <v>41.25</v>
+        <v>66.75</v>
       </c>
       <c r="M62" s="29">
         <f t="shared" si="2"/>
-        <v>20.625</v>
+        <v>33.375</v>
       </c>
       <c r="N62" s="29">
         <f t="shared" si="3"/>
@@ -6106,7 +6180,7 @@
       </c>
       <c r="R62" s="26">
         <f t="shared" si="5"/>
-        <v>33.225000000000001</v>
+        <v>45.975000000000001</v>
       </c>
       <c r="S62" s="1"/>
       <c r="U62" t="s">
@@ -6154,14 +6228,16 @@
         <f t="shared" si="0"/>
         <v>75.5</v>
       </c>
-      <c r="K63" s="1"/>
+      <c r="K63" s="12">
+        <v>70</v>
+      </c>
       <c r="L63" s="29">
         <f t="shared" si="1"/>
-        <v>37.75</v>
+        <v>72.75</v>
       </c>
       <c r="M63" s="29">
         <f t="shared" si="2"/>
-        <v>18.875</v>
+        <v>36.375</v>
       </c>
       <c r="N63" s="29">
         <f t="shared" si="3"/>
@@ -6181,7 +6257,7 @@
       </c>
       <c r="R63" s="26">
         <f t="shared" si="5"/>
-        <v>21.475000000000001</v>
+        <v>38.975000000000001</v>
       </c>
       <c r="S63" s="1"/>
       <c r="U63" t="s">
@@ -6191,7 +6267,7 @@
         <v>122514758</v>
       </c>
     </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C65" t="s">
         <v>169</v>
       </c>
@@ -6221,7 +6297,7 @@
       </c>
       <c r="J65">
         <f t="shared" si="6"/>
-        <v>97</v>
+        <v>97.8</v>
       </c>
       <c r="K65">
         <f t="shared" si="6"/>
@@ -6229,11 +6305,11 @@
       </c>
       <c r="L65">
         <f t="shared" si="6"/>
-        <v>95</v>
+        <v>95.65</v>
       </c>
       <c r="M65">
         <f t="shared" si="6"/>
-        <v>47.5</v>
+        <v>47.825000000000003</v>
       </c>
       <c r="N65">
         <f t="shared" si="6"/>
@@ -6260,7 +6336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C66" t="s">
         <v>170</v>
       </c>
@@ -6294,15 +6370,15 @@
       </c>
       <c r="K66">
         <f t="shared" si="7"/>
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="L66">
         <f t="shared" si="7"/>
-        <v>8.75</v>
+        <v>11</v>
       </c>
       <c r="M66">
         <f t="shared" si="7"/>
-        <v>4.375</v>
+        <v>5.5</v>
       </c>
       <c r="N66">
         <f t="shared" si="7"/>
@@ -6329,78 +6405,76 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="2:22" s="22" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B67" s="15"/>
-      <c r="C67" s="46" t="s">
-        <v>174</v>
-      </c>
-      <c r="D67" s="22">
+    <row r="67" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C67" t="s">
+        <v>171</v>
+      </c>
+      <c r="D67">
         <f>MEDIAN(D5:D63)</f>
         <v>11</v>
       </c>
-      <c r="E67" s="22">
+      <c r="E67">
         <f t="shared" ref="E67:S67" si="8">MEDIAN(E5:E63)</f>
         <v>13.8</v>
       </c>
-      <c r="F67" s="22">
+      <c r="F67">
         <f t="shared" si="8"/>
         <v>12.5</v>
       </c>
-      <c r="G67" s="22">
+      <c r="G67">
         <f t="shared" si="8"/>
         <v>12.5</v>
       </c>
-      <c r="H67" s="22">
+      <c r="H67">
         <f t="shared" si="8"/>
         <v>15</v>
       </c>
-      <c r="I67" s="22">
+      <c r="I67">
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="J67" s="22">
+      <c r="J67">
         <f t="shared" si="8"/>
         <v>72.2</v>
       </c>
-      <c r="K67" s="22">
+      <c r="K67">
         <f t="shared" si="8"/>
-        <v>65</v>
-      </c>
-      <c r="L67" s="22">
+        <v>52.5</v>
+      </c>
+      <c r="L67">
         <f t="shared" si="8"/>
-        <v>44.45</v>
-      </c>
-      <c r="M67" s="22">
+        <v>66.2</v>
+      </c>
+      <c r="M67">
         <f t="shared" si="8"/>
-        <v>22.225000000000001</v>
-      </c>
-      <c r="N67" s="22">
+        <v>33.1</v>
+      </c>
+      <c r="N67">
         <f>MEDIAN(N5:N63)</f>
         <v>4.5999999999999996</v>
       </c>
-      <c r="O67" s="22">
+      <c r="O67">
         <f t="shared" si="8"/>
         <v>23</v>
       </c>
-      <c r="P67" s="22">
+      <c r="P67">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q67" s="22">
+      <c r="Q67">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R67" s="22">
+      <c r="R67">
         <f t="shared" si="8"/>
-        <v>27.875</v>
-      </c>
-      <c r="S67" s="22" t="e">
+        <v>36.774999999999999</v>
+      </c>
+      <c r="S67" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="V67" s="21"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C68" t="s">
         <v>171</v>
       </c>
@@ -6434,15 +6508,15 @@
       </c>
       <c r="K68" cm="1">
         <f t="array" ref="K68">MEDIAN(_xlfn._xlws.FILTER(K5:K63, K5:K63&lt;&gt;0))</f>
-        <v>67</v>
+        <v>53.5</v>
       </c>
       <c r="L68" cm="1">
         <f t="array" ref="L68">MEDIAN(_xlfn._xlws.FILTER(L5:L63, L5:L63&lt;&gt;0))</f>
-        <v>44.85</v>
+        <v>66.75</v>
       </c>
       <c r="M68" cm="1">
         <f t="array" ref="M68">MEDIAN(_xlfn._xlws.FILTER(M5:M63, M5:M63&lt;&gt;0))</f>
-        <v>22.425000000000001</v>
+        <v>33.375</v>
       </c>
       <c r="N68" cm="1">
         <f t="array" ref="N68">MEDIAN(_xlfn._xlws.FILTER(N5:N63, N5:N63&lt;&gt;0))</f>
@@ -6462,7 +6536,7 @@
       </c>
       <c r="R68" cm="1">
         <f t="array" ref="R68">MEDIAN(_xlfn._xlws.FILTER(R5:R63, R5:R63&lt;&gt;0))</f>
-        <v>28.337499999999999</v>
+        <v>38.975000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -6489,1394 +6563,955 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C385ED7-1B36-4BA6-8EF5-792023AA1862}">
-  <dimension ref="A1:F64"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C562E662-4892-4710-BFF6-3FF4023021A9}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="2" max="2" width="26.7109375" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+    </row>
+    <row r="2" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>175</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-    </row>
-    <row r="2" spans="1:6" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="44" t="s">
-        <v>168</v>
-      </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="37" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="37" t="s">
-        <v>164</v>
-      </c>
-      <c r="E3" s="37" t="s">
+      <c r="B3" s="32" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="44">
+        <v>46141</v>
+      </c>
+      <c r="G3" s="44">
+        <v>46142</v>
+      </c>
+      <c r="H3" s="44">
+        <v>46143</v>
+      </c>
+      <c r="I3" s="44">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="12">
+        <v>590029270</v>
+      </c>
+      <c r="D4" s="12">
+        <v>77</v>
+      </c>
+      <c r="E4" s="14">
+        <v>32</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="12">
+        <v>590029204</v>
+      </c>
+      <c r="D5" s="12">
+        <v>77</v>
+      </c>
+      <c r="E5" s="14">
+        <v>29</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="12">
+        <v>590029109</v>
+      </c>
+      <c r="D6" s="12">
+        <v>77</v>
+      </c>
+      <c r="E6" s="14">
+        <v>38</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="12">
+        <v>590029157</v>
+      </c>
+      <c r="D7" s="12">
+        <v>77</v>
+      </c>
+      <c r="E7" s="14">
+        <v>14</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="12">
+        <v>590029274</v>
+      </c>
+      <c r="D8" s="12">
+        <v>77</v>
+      </c>
+      <c r="E8" s="14">
+        <v>8</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="12">
+        <v>590029230</v>
+      </c>
+      <c r="D9" s="12">
+        <v>77</v>
+      </c>
+      <c r="E9" s="14">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="12">
+        <v>590029169</v>
+      </c>
+      <c r="D10" s="12">
+        <v>77</v>
+      </c>
+      <c r="E10" s="14">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="12">
+        <v>590029112</v>
+      </c>
+      <c r="D11" s="12">
+        <v>77</v>
+      </c>
+      <c r="E11" s="14">
+        <v>35</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="12">
+        <v>590029237</v>
+      </c>
+      <c r="D12" s="12">
+        <v>77</v>
+      </c>
+      <c r="E12" s="14">
+        <v>29</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="12">
+        <v>590029079</v>
+      </c>
+      <c r="D13" s="12">
+        <v>77</v>
+      </c>
+      <c r="E13" s="14">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="12">
+        <v>590029145</v>
+      </c>
+      <c r="D14" s="12">
+        <v>77</v>
+      </c>
+      <c r="E14" s="14">
+        <v>23</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="8" t="s">
+      <c r="B15" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="12">
+        <v>590029209</v>
+      </c>
+      <c r="D15" s="12">
+        <v>77</v>
+      </c>
+      <c r="E15" s="14">
+        <v>17</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="12">
+        <v>590027268</v>
+      </c>
+      <c r="D16" s="12">
+        <v>77</v>
+      </c>
+      <c r="E16" s="14">
+        <v>8</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="12">
+        <v>590023855</v>
+      </c>
+      <c r="D17" s="12">
+        <v>77</v>
+      </c>
+      <c r="E17" s="14">
+        <v>29</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18">
         <v>15</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="14">
+      <c r="B18" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="12">
+        <v>590029215</v>
+      </c>
+      <c r="D18" s="12">
+        <v>77</v>
+      </c>
+      <c r="E18" s="14">
+        <v>21</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="12">
+        <v>590029111</v>
+      </c>
+      <c r="D19" s="12">
+        <v>77</v>
+      </c>
+      <c r="E19" s="14">
+        <v>3</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="12">
+        <v>590028683</v>
+      </c>
+      <c r="D20" s="12">
+        <v>77</v>
+      </c>
+      <c r="E20" s="14">
+        <v>23</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="12">
+        <v>590029048</v>
+      </c>
+      <c r="D21" s="12">
+        <v>77</v>
+      </c>
+      <c r="E21" s="14">
+        <v>26</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="12">
+        <v>590029330</v>
+      </c>
+      <c r="D22" s="12">
+        <v>78</v>
+      </c>
+      <c r="E22" s="14">
+        <v>38</v>
+      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="12">
+        <v>590027630</v>
+      </c>
+      <c r="D23" s="12">
+        <v>78</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="12">
+        <v>590029219</v>
+      </c>
+      <c r="D24" s="12">
+        <v>78</v>
+      </c>
+      <c r="E24" s="14">
+        <v>31</v>
+      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="12">
+        <v>590027859</v>
+      </c>
+      <c r="D25" s="12">
+        <v>78</v>
+      </c>
+      <c r="E25" s="14">
+        <v>2</v>
+      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="12">
+        <v>590023917</v>
+      </c>
+      <c r="D26" s="12">
+        <v>78</v>
+      </c>
+      <c r="E26" s="14">
+        <v>4</v>
+      </c>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="12">
+        <v>590023785</v>
+      </c>
+      <c r="D27" s="12">
+        <v>78</v>
+      </c>
+      <c r="E27" s="14">
+        <v>30</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="12">
+        <v>590029264</v>
+      </c>
+      <c r="D28" s="12">
+        <v>78</v>
+      </c>
+      <c r="E28" s="14">
+        <v>12</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" s="12">
+        <v>590029042</v>
+      </c>
+      <c r="D29" s="12">
+        <v>78</v>
+      </c>
+      <c r="E29" s="14">
+        <v>0</v>
+      </c>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" s="12">
+        <v>590029336</v>
+      </c>
+      <c r="D30" s="12">
+        <v>78</v>
+      </c>
+      <c r="E30" s="14">
+        <v>11</v>
+      </c>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" s="12">
+        <v>590029233</v>
+      </c>
+      <c r="D31" s="12">
+        <v>78</v>
+      </c>
+      <c r="E31" s="14">
+        <v>0</v>
+      </c>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" s="12">
+        <v>590029328</v>
+      </c>
+      <c r="D32" s="12">
+        <v>78</v>
+      </c>
+      <c r="E32" s="14">
+        <v>10</v>
+      </c>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="E4" s="5">
-        <f>SUM(D4)</f>
-        <v>100</v>
-      </c>
-      <c r="F4" s="5"/>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="str">
-        <f>Marksheet!A5</f>
-        <v>Aadya Dubey</v>
-      </c>
-      <c r="B5" s="1">
-        <f>Marksheet!B5</f>
-        <v>590029213</v>
-      </c>
-      <c r="C5" s="12">
-        <f>Marksheet!C5</f>
-        <v>77</v>
-      </c>
-      <c r="D5" s="29">
-        <f>Marksheet!K5</f>
-        <v>95.5</v>
-      </c>
-      <c r="E5" s="26">
-        <f>SUM(D5)</f>
-        <v>95.5</v>
-      </c>
-      <c r="F5" s="39"/>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="str">
-        <f>Marksheet!A6</f>
-        <v>Aditya Vishwakarma</v>
-      </c>
-      <c r="B6" s="1">
-        <f>Marksheet!B6</f>
-        <v>590029270</v>
-      </c>
-      <c r="C6" s="12">
-        <f>Marksheet!C6</f>
-        <v>77</v>
-      </c>
-      <c r="D6" s="29">
-        <f>Marksheet!K6</f>
+      <c r="C33" s="12">
+        <v>590028608</v>
+      </c>
+      <c r="D33" s="12">
+        <v>78</v>
+      </c>
+      <c r="E33" s="14">
+        <v>4</v>
+      </c>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>31</v>
+      </c>
+      <c r="B34" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34" s="12">
+        <v>590028605</v>
+      </c>
+      <c r="D34" s="12">
+        <v>78</v>
+      </c>
+      <c r="E34" s="14">
+        <v>0</v>
+      </c>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>32</v>
+      </c>
+      <c r="B35" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" s="12">
+        <v>590026626</v>
+      </c>
+      <c r="D35" s="12">
+        <v>78</v>
+      </c>
+      <c r="E35" s="14">
+        <v>0</v>
+      </c>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>33</v>
+      </c>
+      <c r="B36" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="12">
+        <v>590029319</v>
+      </c>
+      <c r="D36" s="12">
+        <v>78</v>
+      </c>
+      <c r="E36" s="14">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>34</v>
+      </c>
+      <c r="B37" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="C37" s="12">
+        <v>590029339</v>
+      </c>
+      <c r="D37" s="12">
+        <v>78</v>
+      </c>
+      <c r="E37" s="14">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>35</v>
+      </c>
+      <c r="B38" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="C38" s="12">
+        <v>590029148</v>
+      </c>
+      <c r="D38" s="12">
+        <v>78</v>
+      </c>
+      <c r="E38" s="14">
+        <v>17</v>
+      </c>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>36</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39" s="12">
+        <v>590029309</v>
+      </c>
+      <c r="D39" s="12">
+        <v>78</v>
+      </c>
+      <c r="E39" s="14">
+        <v>17</v>
+      </c>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>37</v>
+      </c>
+      <c r="B40" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C40" s="12">
+        <v>590028838</v>
+      </c>
+      <c r="D40" s="12">
+        <v>78</v>
+      </c>
+      <c r="E40" s="14">
+        <v>0</v>
+      </c>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>38</v>
+      </c>
+      <c r="B41" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C41" s="12">
+        <v>590029107</v>
+      </c>
+      <c r="D41" s="12">
+        <v>78</v>
+      </c>
+      <c r="E41" s="14">
+        <v>22</v>
+      </c>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42">
         <v>39</v>
       </c>
-      <c r="E6" s="26">
-        <f t="shared" ref="E6:E64" si="0">SUM(D6)</f>
-        <v>39</v>
-      </c>
-      <c r="F6" s="39"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="str">
-        <f>Marksheet!A7</f>
-        <v>Arjun</v>
-      </c>
-      <c r="B7" s="1">
-        <f>Marksheet!B7</f>
-        <v>590029204</v>
-      </c>
-      <c r="C7" s="12">
-        <f>Marksheet!C7</f>
-        <v>77</v>
-      </c>
-      <c r="D7" s="29">
-        <f>Marksheet!K7</f>
-        <v>73.5</v>
-      </c>
-      <c r="E7" s="26">
-        <f t="shared" si="0"/>
-        <v>73.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="str">
-        <f>Marksheet!A8</f>
-        <v>Aryan Yadav</v>
-      </c>
-      <c r="B8" s="1">
-        <f>Marksheet!B8</f>
-        <v>590029109</v>
-      </c>
-      <c r="C8" s="12">
-        <f>Marksheet!C8</f>
-        <v>77</v>
-      </c>
-      <c r="D8" s="29">
-        <f>Marksheet!K8</f>
-        <v>54.5</v>
-      </c>
-      <c r="E8" s="26">
-        <f t="shared" si="0"/>
-        <v>54.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="str">
-        <f>Marksheet!A9</f>
-        <v>Astik Patel</v>
-      </c>
-      <c r="B9" s="1">
-        <f>Marksheet!B9</f>
-        <v>590029070</v>
-      </c>
-      <c r="C9" s="12">
-        <f>Marksheet!C9</f>
-        <v>77</v>
-      </c>
-      <c r="D9" s="29">
-        <f>Marksheet!K9</f>
-        <v>97.5</v>
-      </c>
-      <c r="E9" s="26">
-        <f t="shared" si="0"/>
-        <v>97.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="str">
-        <f>Marksheet!A10</f>
-        <v>Ayush Mohan</v>
-      </c>
-      <c r="B10" s="1">
-        <f>Marksheet!B10</f>
-        <v>590029157</v>
-      </c>
-      <c r="C10" s="12">
-        <f>Marksheet!C10</f>
-        <v>77</v>
-      </c>
-      <c r="D10" s="29">
-        <f>Marksheet!K10</f>
+      <c r="B42" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="C42" s="12">
+        <v>590029266</v>
+      </c>
+      <c r="D42" s="12">
+        <v>78</v>
+      </c>
+      <c r="E42" s="14">
+        <v>9</v>
+      </c>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43">
         <v>40</v>
       </c>
-      <c r="E10" s="26">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="str">
-        <f>Marksheet!A11</f>
-        <v>Bhanu Purohit</v>
-      </c>
-      <c r="B11" s="1">
-        <f>Marksheet!B11</f>
-        <v>590027157</v>
-      </c>
-      <c r="C11" s="12">
-        <f>Marksheet!C11</f>
-        <v>77</v>
-      </c>
-      <c r="D11" s="29">
-        <f>Marksheet!K11</f>
-        <v>54</v>
-      </c>
-      <c r="E11" s="26">
-        <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="str">
-        <f>Marksheet!A12</f>
-        <v>Biswabandya Mohanty</v>
-      </c>
-      <c r="B12" s="1">
-        <f>Marksheet!B12</f>
-        <v>590029274</v>
-      </c>
-      <c r="C12" s="12">
-        <f>Marksheet!C12</f>
-        <v>77</v>
-      </c>
-      <c r="D12" s="29">
-        <f>Marksheet!K12</f>
-        <v>44.5</v>
-      </c>
-      <c r="E12" s="26">
-        <f t="shared" si="0"/>
-        <v>44.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="str">
-        <f>Marksheet!A13</f>
-        <v>Eashan Vashisht</v>
-      </c>
-      <c r="B13" s="1">
-        <f>Marksheet!B13</f>
-        <v>590028572</v>
-      </c>
-      <c r="C13" s="12">
-        <f>Marksheet!C13</f>
-        <v>77</v>
-      </c>
-      <c r="D13" s="29">
-        <f>Marksheet!K13</f>
-        <v>98</v>
-      </c>
-      <c r="E13" s="26">
-        <f t="shared" si="0"/>
-        <v>98</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="str">
-        <f>Marksheet!A14</f>
-        <v>Hardik Joshi</v>
-      </c>
-      <c r="B14" s="1">
-        <f>Marksheet!B14</f>
-        <v>590029230</v>
-      </c>
-      <c r="C14" s="12">
-        <f>Marksheet!C14</f>
-        <v>77</v>
-      </c>
-      <c r="D14" s="29">
-        <f>Marksheet!K14</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="str">
-        <f>Marksheet!A15</f>
-        <v>Hrithvik Bhardwaj</v>
-      </c>
-      <c r="B15" s="1">
-        <f>Marksheet!B15</f>
-        <v>590029169</v>
-      </c>
-      <c r="C15" s="12">
-        <f>Marksheet!C15</f>
-        <v>77</v>
-      </c>
-      <c r="D15" s="29">
-        <f>Marksheet!K15</f>
-        <v>39</v>
-      </c>
-      <c r="E15" s="26">
-        <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="str">
-        <f>Marksheet!A16</f>
-        <v>Nitish Kumar</v>
-      </c>
-      <c r="B16" s="1">
-        <f>Marksheet!B16</f>
-        <v>590029112</v>
-      </c>
-      <c r="C16" s="12">
-        <f>Marksheet!C16</f>
-        <v>77</v>
-      </c>
-      <c r="D16" s="29">
-        <f>Marksheet!K16</f>
-        <v>65</v>
-      </c>
-      <c r="E16" s="26">
-        <f t="shared" si="0"/>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="str">
-        <f>Marksheet!A17</f>
-        <v>Omkareshwar Chaubey</v>
-      </c>
-      <c r="B17" s="1">
-        <f>Marksheet!B17</f>
-        <v>590025556</v>
-      </c>
-      <c r="C17" s="12">
-        <f>Marksheet!C17</f>
-        <v>77</v>
-      </c>
-      <c r="D17" s="29">
-        <f>Marksheet!K17</f>
-        <v>68.5</v>
-      </c>
-      <c r="E17" s="26">
-        <f t="shared" si="0"/>
-        <v>68.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="str">
-        <f>Marksheet!A18</f>
-        <v>Pavani Jain</v>
-      </c>
-      <c r="B18" s="1">
-        <f>Marksheet!B18</f>
-        <v>590027830</v>
-      </c>
-      <c r="C18" s="12">
-        <f>Marksheet!C18</f>
-        <v>77</v>
-      </c>
-      <c r="D18" s="29">
-        <f>Marksheet!K18</f>
-        <v>85.5</v>
-      </c>
-      <c r="E18" s="26">
-        <f t="shared" si="0"/>
-        <v>85.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="str">
-        <f>Marksheet!A19</f>
-        <v>Prapti Uniyal</v>
-      </c>
-      <c r="B19" s="1">
-        <f>Marksheet!B19</f>
-        <v>590028360</v>
-      </c>
-      <c r="C19" s="12">
-        <f>Marksheet!C19</f>
-        <v>77</v>
-      </c>
-      <c r="D19" s="29">
-        <f>Marksheet!K19</f>
-        <v>84.5</v>
-      </c>
-      <c r="E19" s="26">
-        <f t="shared" si="0"/>
-        <v>84.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="str">
-        <f>Marksheet!A20</f>
-        <v>Priyadarshi Prabhakar</v>
-      </c>
-      <c r="B20" s="1">
-        <f>Marksheet!B20</f>
-        <v>590029237</v>
-      </c>
-      <c r="C20" s="12">
-        <f>Marksheet!C20</f>
-        <v>77</v>
-      </c>
-      <c r="D20" s="29">
-        <f>Marksheet!K20</f>
-        <v>51</v>
-      </c>
-      <c r="E20" s="26">
-        <f t="shared" si="0"/>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="str">
-        <f>Marksheet!A21</f>
-        <v>Radhe Patel</v>
-      </c>
-      <c r="B21" s="1">
-        <f>Marksheet!B21</f>
-        <v>590029079</v>
-      </c>
-      <c r="C21" s="12">
-        <f>Marksheet!C21</f>
-        <v>77</v>
-      </c>
-      <c r="D21" s="29">
-        <f>Marksheet!K21</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="str">
-        <f>Marksheet!A22</f>
-        <v>Rishika Purushotham</v>
-      </c>
-      <c r="B22" s="1">
-        <f>Marksheet!B22</f>
-        <v>590029145</v>
-      </c>
-      <c r="C22" s="12">
-        <f>Marksheet!C22</f>
-        <v>77</v>
-      </c>
-      <c r="D22" s="29">
-        <f>Marksheet!K22</f>
-        <v>67</v>
-      </c>
-      <c r="E22" s="26">
-        <f t="shared" si="0"/>
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="str">
-        <f>Marksheet!A23</f>
-        <v>Rishiv Kumar</v>
-      </c>
-      <c r="B23" s="1">
-        <f>Marksheet!B23</f>
-        <v>590029209</v>
-      </c>
-      <c r="C23" s="12">
-        <f>Marksheet!C23</f>
-        <v>77</v>
-      </c>
-      <c r="D23" s="29">
-        <f>Marksheet!K23</f>
-        <v>28</v>
-      </c>
-      <c r="E23" s="26">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="str">
-        <f>Marksheet!A24</f>
-        <v>Sankalp Sunil Ronge</v>
-      </c>
-      <c r="B24" s="1">
-        <f>Marksheet!B24</f>
-        <v>590027268</v>
-      </c>
-      <c r="C24" s="12">
-        <f>Marksheet!C24</f>
-        <v>77</v>
-      </c>
-      <c r="D24" s="29">
-        <f>Marksheet!K24</f>
-        <v>46.5</v>
-      </c>
-      <c r="E24" s="26">
-        <f t="shared" si="0"/>
-        <v>46.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="str">
-        <f>Marksheet!A25</f>
-        <v>Sartaj Singh</v>
-      </c>
-      <c r="B25" s="1">
-        <f>Marksheet!B25</f>
-        <v>590029227</v>
-      </c>
-      <c r="C25" s="12">
-        <f>Marksheet!C25</f>
-        <v>77</v>
-      </c>
-      <c r="D25" s="29">
-        <f>Marksheet!K25</f>
-        <v>93.5</v>
-      </c>
-      <c r="E25" s="26">
-        <f t="shared" si="0"/>
-        <v>93.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="str">
-        <f>Marksheet!A26</f>
-        <v>Satakshi Gupta</v>
-      </c>
-      <c r="B26" s="1">
-        <f>Marksheet!B26</f>
-        <v>590029241</v>
-      </c>
-      <c r="C26" s="12">
-        <f>Marksheet!C26</f>
-        <v>77</v>
-      </c>
-      <c r="D26" s="29">
-        <f>Marksheet!K26</f>
-        <v>76</v>
-      </c>
-      <c r="E26" s="26">
-        <f t="shared" si="0"/>
-        <v>76</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="str">
-        <f>Marksheet!A27</f>
-        <v>Shaswat Shantanu</v>
-      </c>
-      <c r="B27" s="1">
-        <f>Marksheet!B27</f>
-        <v>590023855</v>
-      </c>
-      <c r="C27" s="12">
-        <f>Marksheet!C27</f>
-        <v>77</v>
-      </c>
-      <c r="D27" s="29">
-        <f>Marksheet!K27</f>
-        <v>29</v>
-      </c>
-      <c r="E27" s="26">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="str">
-        <f>Marksheet!A28</f>
-        <v>Siddhant Rai</v>
-      </c>
-      <c r="B28" s="1">
-        <f>Marksheet!B28</f>
-        <v>590029215</v>
-      </c>
-      <c r="C28" s="12">
-        <f>Marksheet!C28</f>
-        <v>77</v>
-      </c>
-      <c r="D28" s="29">
-        <f>Marksheet!K28</f>
-        <v>52.5</v>
-      </c>
-      <c r="E28" s="26">
-        <f t="shared" si="0"/>
-        <v>52.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="str">
-        <f>Marksheet!A29</f>
-        <v>Sidhaant Singh Jyrwa</v>
-      </c>
-      <c r="B29" s="1">
-        <f>Marksheet!B29</f>
-        <v>590029111</v>
-      </c>
-      <c r="C29" s="12">
-        <f>Marksheet!C29</f>
-        <v>77</v>
-      </c>
-      <c r="D29" s="29">
-        <f>Marksheet!K29</f>
-        <v>45</v>
-      </c>
-      <c r="E29" s="26">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="str">
-        <f>Marksheet!A30</f>
-        <v>Subrat Singh Jadaun</v>
-      </c>
-      <c r="B30" s="1">
-        <f>Marksheet!B30</f>
-        <v>590028683</v>
-      </c>
-      <c r="C30" s="12">
-        <f>Marksheet!C30</f>
-        <v>77</v>
-      </c>
-      <c r="D30" s="29">
-        <f>Marksheet!K30</f>
-        <v>78.5</v>
-      </c>
-      <c r="E30" s="26">
-        <f t="shared" si="0"/>
-        <v>78.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="str">
-        <f>Marksheet!A31</f>
-        <v>Tushita Sharma</v>
-      </c>
-      <c r="B31" s="1">
-        <f>Marksheet!B31</f>
-        <v>590029121</v>
-      </c>
-      <c r="C31" s="12">
-        <f>Marksheet!C31</f>
-        <v>77</v>
-      </c>
-      <c r="D31" s="29">
-        <f>Marksheet!K31</f>
-        <v>90.5</v>
-      </c>
-      <c r="E31" s="26">
-        <f t="shared" si="0"/>
-        <v>90.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="str">
-        <f>Marksheet!A32</f>
-        <v>Vaishnavi Kumari</v>
-      </c>
-      <c r="B32" s="1">
-        <f>Marksheet!B32</f>
-        <v>590029048</v>
-      </c>
-      <c r="C32" s="12">
-        <f>Marksheet!C32</f>
-        <v>77</v>
-      </c>
-      <c r="D32" s="29">
-        <f>Marksheet!K32</f>
-        <v>83</v>
-      </c>
-      <c r="E32" s="26">
-        <f t="shared" si="0"/>
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="str">
-        <f>Marksheet!A33</f>
-        <v>Vivek Chauhan</v>
-      </c>
-      <c r="B33" s="1">
-        <f>Marksheet!B33</f>
-        <v>590029184</v>
-      </c>
-      <c r="C33" s="12">
-        <f>Marksheet!C33</f>
-        <v>77</v>
-      </c>
-      <c r="D33" s="29">
-        <f>Marksheet!K33</f>
-        <v>75.5</v>
-      </c>
-      <c r="E33" s="26">
-        <f t="shared" si="0"/>
-        <v>75.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="str">
-        <f>Marksheet!A34</f>
-        <v>Aadarshi Bisht</v>
-      </c>
-      <c r="B34" s="1">
-        <f>Marksheet!B34</f>
-        <v>590029330</v>
-      </c>
-      <c r="C34" s="12">
-        <f>Marksheet!C34</f>
+      <c r="B43" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="C43" s="12">
+        <v>590029349</v>
+      </c>
+      <c r="D43" s="12">
         <v>78</v>
       </c>
-      <c r="D34" s="29">
-        <f>Marksheet!K34</f>
-        <v>0</v>
-      </c>
-      <c r="E34" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="str">
-        <f>Marksheet!A35</f>
-        <v>Aarush Prasad</v>
-      </c>
-      <c r="B35" s="1">
-        <f>Marksheet!B35</f>
-        <v>590027630</v>
-      </c>
-      <c r="C35" s="12">
-        <f>Marksheet!C35</f>
+      <c r="E43" s="14">
+        <v>31</v>
+      </c>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>41</v>
+      </c>
+      <c r="B44" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="C44" s="12">
+        <v>590029353</v>
+      </c>
+      <c r="D44" s="12">
         <v>78</v>
       </c>
-      <c r="D35" s="29">
-        <f>Marksheet!K35</f>
-        <v>0</v>
-      </c>
-      <c r="E35" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="str">
-        <f>Marksheet!A36</f>
-        <v>Aditya Mishra</v>
-      </c>
-      <c r="B36" s="1">
-        <f>Marksheet!B36</f>
-        <v>590029219</v>
-      </c>
-      <c r="C36" s="12">
-        <f>Marksheet!C36</f>
-        <v>78</v>
-      </c>
-      <c r="D36" s="29">
-        <f>Marksheet!K36</f>
-        <v>0</v>
-      </c>
-      <c r="E36" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="str">
-        <f>Marksheet!A37</f>
-        <v>Aman Barnwal</v>
-      </c>
-      <c r="B37" s="1">
-        <f>Marksheet!B37</f>
-        <v>590028933</v>
-      </c>
-      <c r="C37" s="12">
-        <f>Marksheet!C37</f>
-        <v>78</v>
-      </c>
-      <c r="D37" s="29">
-        <f>Marksheet!K37</f>
-        <v>0</v>
-      </c>
-      <c r="E37" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="str">
-        <f>Marksheet!A38</f>
-        <v>Ashutosh Shrivastava</v>
-      </c>
-      <c r="B38" s="1">
-        <f>Marksheet!B38</f>
-        <v>590027859</v>
-      </c>
-      <c r="C38" s="12">
-        <f>Marksheet!C38</f>
-        <v>78</v>
-      </c>
-      <c r="D38" s="29">
-        <f>Marksheet!K38</f>
-        <v>0</v>
-      </c>
-      <c r="E38" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="str">
-        <f>Marksheet!A39</f>
-        <v>Ayan Pande</v>
-      </c>
-      <c r="B39" s="1">
-        <f>Marksheet!B39</f>
-        <v>590028682</v>
-      </c>
-      <c r="C39" s="12">
-        <f>Marksheet!C39</f>
-        <v>78</v>
-      </c>
-      <c r="D39" s="29">
-        <f>Marksheet!K39</f>
-        <v>0</v>
-      </c>
-      <c r="E39" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="str">
-        <f>Marksheet!A40</f>
-        <v>Ayush Pratap Singh</v>
-      </c>
-      <c r="B40" s="1">
-        <f>Marksheet!B40</f>
-        <v>590023917</v>
-      </c>
-      <c r="C40" s="12">
-        <f>Marksheet!C40</f>
-        <v>78</v>
-      </c>
-      <c r="D40" s="29">
-        <f>Marksheet!K40</f>
-        <v>0</v>
-      </c>
-      <c r="E40" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="str">
-        <f>Marksheet!A41</f>
-        <v>Gayatri Bhatt</v>
-      </c>
-      <c r="B41" s="1">
-        <f>Marksheet!B41</f>
-        <v>590023785</v>
-      </c>
-      <c r="C41" s="12">
-        <f>Marksheet!C41</f>
-        <v>78</v>
-      </c>
-      <c r="D41" s="29">
-        <f>Marksheet!K41</f>
-        <v>0</v>
-      </c>
-      <c r="E41" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="str">
-        <f>Marksheet!A42</f>
-        <v>Harsh Mudgal</v>
-      </c>
-      <c r="B42" s="1">
-        <f>Marksheet!B42</f>
-        <v>590029264</v>
-      </c>
-      <c r="C42" s="12">
-        <f>Marksheet!C42</f>
-        <v>78</v>
-      </c>
-      <c r="D42" s="29">
-        <f>Marksheet!K42</f>
-        <v>0</v>
-      </c>
-      <c r="E42" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="str">
-        <f>Marksheet!A43</f>
-        <v>Kanan Nidhania</v>
-      </c>
-      <c r="B43" s="1">
-        <f>Marksheet!B43</f>
-        <v>590029042</v>
-      </c>
-      <c r="C43" s="12">
-        <f>Marksheet!C43</f>
-        <v>78</v>
-      </c>
-      <c r="D43" s="29">
-        <f>Marksheet!K43</f>
-        <v>0</v>
-      </c>
-      <c r="E43" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="str">
-        <f>Marksheet!A44</f>
-        <v>Kanishka Diwakar</v>
-      </c>
-      <c r="B44" s="1">
-        <f>Marksheet!B44</f>
-        <v>590029336</v>
-      </c>
-      <c r="C44" s="12">
-        <f>Marksheet!C44</f>
-        <v>78</v>
-      </c>
-      <c r="D44" s="29">
-        <f>Marksheet!K44</f>
-        <v>0</v>
-      </c>
-      <c r="E44" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="str">
-        <f>Marksheet!A45</f>
-        <v>Keshav Chahda</v>
-      </c>
-      <c r="B45" s="1">
-        <f>Marksheet!B45</f>
-        <v>590029233</v>
-      </c>
-      <c r="C45" s="12">
-        <f>Marksheet!C45</f>
-        <v>78</v>
-      </c>
-      <c r="D45" s="29">
-        <f>Marksheet!K45</f>
-        <v>0</v>
-      </c>
-      <c r="E45" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="str">
-        <f>Marksheet!A46</f>
-        <v>Lakshay Dhanda</v>
-      </c>
-      <c r="B46" s="1">
-        <f>Marksheet!B46</f>
-        <v>590029328</v>
-      </c>
-      <c r="C46" s="12">
-        <f>Marksheet!C46</f>
-        <v>78</v>
-      </c>
-      <c r="D46" s="29">
-        <f>Marksheet!K46</f>
-        <v>0</v>
-      </c>
-      <c r="E46" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="str">
-        <f>Marksheet!A47</f>
-        <v>Lakshya Singh</v>
-      </c>
-      <c r="B47" s="1">
-        <f>Marksheet!B47</f>
-        <v>590028608</v>
-      </c>
-      <c r="C47" s="12">
-        <f>Marksheet!C47</f>
-        <v>78</v>
-      </c>
-      <c r="D47" s="29">
-        <f>Marksheet!K47</f>
-        <v>0</v>
-      </c>
-      <c r="E47" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="str">
-        <f>Marksheet!A48</f>
-        <v>Mayank Chand Ramola</v>
-      </c>
-      <c r="B48" s="1">
-        <f>Marksheet!B48</f>
-        <v>590028605</v>
-      </c>
-      <c r="C48" s="12">
-        <f>Marksheet!C48</f>
-        <v>78</v>
-      </c>
-      <c r="D48" s="29">
-        <f>Marksheet!K48</f>
-        <v>0</v>
-      </c>
-      <c r="E48" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="str">
-        <f>Marksheet!A49</f>
-        <v>Mukesh Patel</v>
-      </c>
-      <c r="B49" s="1">
-        <f>Marksheet!B49</f>
-        <v>590026626</v>
-      </c>
-      <c r="C49" s="12">
-        <f>Marksheet!C49</f>
-        <v>78</v>
-      </c>
-      <c r="D49" s="29">
-        <f>Marksheet!K49</f>
-        <v>0</v>
-      </c>
-      <c r="E49" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="str">
-        <f>Marksheet!A50</f>
-        <v>Nipun Singh</v>
-      </c>
-      <c r="B50" s="1">
-        <f>Marksheet!B50</f>
-        <v>590029310</v>
-      </c>
-      <c r="C50" s="12">
-        <f>Marksheet!C50</f>
-        <v>78</v>
-      </c>
-      <c r="D50" s="29">
-        <f>Marksheet!K50</f>
-        <v>0</v>
-      </c>
-      <c r="E50" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="str">
-        <f>Marksheet!A51</f>
-        <v>Paras Bhall</v>
-      </c>
-      <c r="B51" s="1">
-        <f>Marksheet!B51</f>
-        <v>590029319</v>
-      </c>
-      <c r="C51" s="12">
-        <f>Marksheet!C51</f>
-        <v>78</v>
-      </c>
-      <c r="D51" s="29">
-        <f>Marksheet!K51</f>
-        <v>0</v>
-      </c>
-      <c r="E51" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="str">
-        <f>Marksheet!A52</f>
-        <v>Raghav Kumar Goyal</v>
-      </c>
-      <c r="B52" s="1">
-        <f>Marksheet!B52</f>
-        <v>590029339</v>
-      </c>
-      <c r="C52" s="12">
-        <f>Marksheet!C52</f>
-        <v>78</v>
-      </c>
-      <c r="D52" s="29">
-        <f>Marksheet!K52</f>
-        <v>0</v>
-      </c>
-      <c r="E52" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="str">
-        <f>Marksheet!A53</f>
-        <v>Rahul</v>
-      </c>
-      <c r="B53" s="1">
-        <f>Marksheet!B53</f>
-        <v>590029148</v>
-      </c>
-      <c r="C53" s="12">
-        <f>Marksheet!C53</f>
-        <v>78</v>
-      </c>
-      <c r="D53" s="29">
-        <f>Marksheet!K53</f>
-        <v>0</v>
-      </c>
-      <c r="E53" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="str">
-        <f>Marksheet!A54</f>
-        <v>Rahul Singh</v>
-      </c>
-      <c r="B54" s="1">
-        <f>Marksheet!B54</f>
-        <v>590029309</v>
-      </c>
-      <c r="C54" s="12">
-        <f>Marksheet!C54</f>
-        <v>78</v>
-      </c>
-      <c r="D54" s="29">
-        <f>Marksheet!K54</f>
-        <v>0</v>
-      </c>
-      <c r="E54" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="str">
-        <f>Marksheet!A55</f>
-        <v>Satyam Singh</v>
-      </c>
-      <c r="B55" s="1">
-        <f>Marksheet!B55</f>
-        <v>590028838</v>
-      </c>
-      <c r="C55" s="12">
-        <f>Marksheet!C55</f>
-        <v>78</v>
-      </c>
-      <c r="D55" s="29">
-        <f>Marksheet!K55</f>
-        <v>0</v>
-      </c>
-      <c r="E55" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="str">
-        <f>Marksheet!A56</f>
-        <v>Shashwat Agrawal</v>
-      </c>
-      <c r="B56" s="1">
-        <f>Marksheet!B56</f>
-        <v>590029107</v>
-      </c>
-      <c r="C56" s="12">
-        <f>Marksheet!C56</f>
-        <v>78</v>
-      </c>
-      <c r="D56" s="29">
-        <f>Marksheet!K56</f>
-        <v>0</v>
-      </c>
-      <c r="E56" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="str">
-        <f>Marksheet!A57</f>
-        <v>Siddhant Gurung</v>
-      </c>
-      <c r="B57" s="1">
-        <f>Marksheet!B57</f>
-        <v>590029266</v>
-      </c>
-      <c r="C57" s="12">
-        <f>Marksheet!C57</f>
-        <v>78</v>
-      </c>
-      <c r="D57" s="29">
-        <f>Marksheet!K57</f>
-        <v>0</v>
-      </c>
-      <c r="E57" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="str">
-        <f>Marksheet!A58</f>
-        <v>Simarjot Kaur Gill</v>
-      </c>
-      <c r="B58" s="1">
-        <f>Marksheet!B58</f>
-        <v>590029354</v>
-      </c>
-      <c r="C58" s="12">
-        <f>Marksheet!C58</f>
-        <v>78</v>
-      </c>
-      <c r="D58" s="29">
-        <f>Marksheet!K58</f>
-        <v>0</v>
-      </c>
-      <c r="E58" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="str">
-        <f>Marksheet!A59</f>
-        <v>Tanishq Bansal</v>
-      </c>
-      <c r="B59" s="1">
-        <f>Marksheet!B59</f>
-        <v>590029349</v>
-      </c>
-      <c r="C59" s="12">
-        <f>Marksheet!C59</f>
-        <v>78</v>
-      </c>
-      <c r="D59" s="29">
-        <f>Marksheet!K59</f>
-        <v>0</v>
-      </c>
-      <c r="E59" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="str">
-        <f>Marksheet!A60</f>
-        <v>Tanmay Amit Verma</v>
-      </c>
-      <c r="B60" s="1">
-        <f>Marksheet!B60</f>
-        <v>590029302</v>
-      </c>
-      <c r="C60" s="12">
-        <f>Marksheet!C60</f>
-        <v>78</v>
-      </c>
-      <c r="D60" s="29">
-        <f>Marksheet!K60</f>
-        <v>0</v>
-      </c>
-      <c r="E60" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="str">
-        <f>Marksheet!A61</f>
-        <v>Vandana Yadav</v>
-      </c>
-      <c r="B61" s="1">
-        <f>Marksheet!B61</f>
-        <v>590029262</v>
-      </c>
-      <c r="C61" s="12">
-        <f>Marksheet!C61</f>
-        <v>78</v>
-      </c>
-      <c r="D61" s="29">
-        <f>Marksheet!K61</f>
-        <v>0</v>
-      </c>
-      <c r="E61" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="str">
-        <f>Marksheet!A62</f>
-        <v>Vidit Ahuja</v>
-      </c>
-      <c r="B62" s="1">
-        <f>Marksheet!B62</f>
-        <v>590029285</v>
-      </c>
-      <c r="C62" s="12">
-        <f>Marksheet!C62</f>
-        <v>78</v>
-      </c>
-      <c r="D62" s="29">
-        <f>Marksheet!K62</f>
-        <v>0</v>
-      </c>
-      <c r="E62" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="str">
-        <f>Marksheet!A63</f>
-        <v>Vinit Kumar</v>
-      </c>
-      <c r="B63" s="1">
-        <f>Marksheet!B63</f>
-        <v>590029353</v>
-      </c>
-      <c r="C63" s="12">
-        <f>Marksheet!C63</f>
-        <v>78</v>
-      </c>
-      <c r="D63" s="29">
-        <f>Marksheet!K63</f>
-        <v>0</v>
-      </c>
-      <c r="E63" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="29"/>
-      <c r="E64" s="26"/>
+      <c r="E44" s="14">
+        <v>13</v>
+      </c>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="F2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E64">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="84" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10426,45 +10061,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="47" t="s">
         <v>162</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
     </row>
     <row r="2" spans="1:21" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="44" t="str">
+      <c r="A2" s="47" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Physics for Computer Engineers (PHYS 1036) </v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -14057,47 +13692,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
     </row>
     <row r="2" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="44" t="str">
+      <c r="A2" s="47" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Physics for Computer Engineers (PHYS 1036) </v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="45"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -17377,45 +17012,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="47" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
     </row>
     <row r="2" spans="1:21" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="44" t="str">
+      <c r="A2" s="47" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Physics for Computer Engineers (PHYS 1036) </v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -20946,43 +20581,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
     </row>
     <row r="2" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="44" t="str">
+      <c r="A2" s="47" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Physics for Computer Engineers (PHYS 1036) </v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="16"/>
@@ -21969,64 +21604,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="47" t="s">
         <v>163</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
     </row>
     <row r="2" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="44" t="str">
+      <c r="A2" s="47" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Physics for Computer Engineers (PHYS 1036) </v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>152</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>137</v>
@@ -22035,7 +21670,7 @@
         <v>152</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>152</v>
@@ -22051,7 +21686,7 @@
         <v>152</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -25651,43 +25286,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
     </row>
     <row r="2" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="44" t="str">
+      <c r="A2" s="47" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Physics for Computer Engineers (PHYS 1036) </v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -29489,47 +29124,47 @@
     <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="13" width="4.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="8.28515625" customWidth="1"/>
-    <col min="15" max="15" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
     </row>
     <row r="2" spans="1:21" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="44" t="str">
+      <c r="A2" s="47" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Physics for Computer Engineers (PHYS 1036) </v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -29544,10 +29179,10 @@
         <v>152</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -29564,7 +29199,7 @@
         <v>152</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -30626,25 +30261,40 @@
         <f>'Mid Sem'!A26</f>
         <v>Sartaj Singh</v>
       </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26">
+        <v>3</v>
+      </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26">
+        <v>3</v>
+      </c>
       <c r="N26" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R26" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S26" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T26" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U26">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -32241,45 +31891,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
     </row>
     <row r="2" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="44" t="str">
+      <c r="A2" s="47" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Physics for Computer Engineers (PHYS 1036) </v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -32292,13 +31942,13 @@
         <v>137</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>152</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>152</v>
@@ -32317,7 +31967,7 @@
         <v>152</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -32467,19 +32117,19 @@
         <v>15</v>
       </c>
       <c r="P6" s="1"/>
-      <c r="S6" s="43">
+      <c r="S6" s="46">
         <f t="shared" ref="S6:S65" si="0">SUM(D6:E6)</f>
         <v>3.5</v>
       </c>
-      <c r="T6" s="43">
+      <c r="T6" s="46">
         <f t="shared" ref="T6:T65" si="1">SUM(G6,I6)</f>
         <v>4</v>
       </c>
-      <c r="U6" s="43">
+      <c r="U6" s="46">
         <f t="shared" ref="U6:U65" si="2">SUM(F6,H6)</f>
         <v>7.5</v>
       </c>
-      <c r="V6" s="43">
+      <c r="V6" s="46">
         <f t="shared" ref="V6:V65" si="3">SUM(S6:U6)</f>
         <v>15</v>
       </c>
@@ -32524,19 +32174,19 @@
         <v>11.5</v>
       </c>
       <c r="P7" s="1"/>
-      <c r="S7" s="43">
+      <c r="S7" s="46">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="T7" s="43">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="U7" s="43">
+      <c r="T7" s="46">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="U7" s="46">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="V7" s="43">
+      <c r="V7" s="46">
         <f t="shared" si="3"/>
         <v>11.5</v>
       </c>
@@ -32581,19 +32231,19 @@
         <v>11.5</v>
       </c>
       <c r="P8" s="1"/>
-      <c r="S8" s="43">
+      <c r="S8" s="46">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T8" s="43">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="U8" s="43">
+      <c r="T8" s="46">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="U8" s="46">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="V8" s="43">
+      <c r="V8" s="46">
         <f t="shared" si="3"/>
         <v>11.5</v>
       </c>
@@ -32610,12 +32260,24 @@
       <c r="C9" s="27" t="b">
         <v>0</v>
       </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
+      <c r="D9" s="1">
+        <v>2</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2</v>
+      </c>
+      <c r="F9" s="1">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2</v>
+      </c>
+      <c r="H9" s="1">
+        <v>6</v>
+      </c>
+      <c r="I9" s="1">
+        <v>6</v>
+      </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -32626,21 +32288,21 @@
         <v>0</v>
       </c>
       <c r="P9" s="1"/>
-      <c r="S9" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T9" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U9" s="43">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V9" s="43">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="S9" s="46">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="T9" s="46">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="U9" s="46">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="V9" s="46">
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
@@ -32683,19 +32345,19 @@
         <v>17.5</v>
       </c>
       <c r="P10" s="1"/>
-      <c r="S10" s="43">
+      <c r="S10" s="46">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T10" s="43">
+      <c r="T10" s="46">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="U10" s="43">
+      <c r="U10" s="46">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V10" s="43">
+      <c r="V10" s="46">
         <f t="shared" si="3"/>
         <v>17.5</v>
       </c>
@@ -32740,19 +32402,19 @@
         <v>15.5</v>
       </c>
       <c r="P11" s="1"/>
-      <c r="S11" s="43">
+      <c r="S11" s="46">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T11" s="43">
+      <c r="T11" s="46">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="U11" s="43">
+      <c r="U11" s="46">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="V11" s="43">
+      <c r="V11" s="46">
         <f t="shared" si="3"/>
         <v>15.5</v>
       </c>
@@ -32769,12 +32431,24 @@
       <c r="C12" s="27" t="b">
         <v>0</v>
       </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+      <c r="D12" s="1">
+        <v>2</v>
+      </c>
+      <c r="E12" s="1">
+        <v>2</v>
+      </c>
+      <c r="F12" s="1">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2</v>
+      </c>
+      <c r="H12" s="1">
+        <v>6</v>
+      </c>
+      <c r="I12" s="1">
+        <v>6</v>
+      </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -32785,21 +32459,21 @@
         <v>0</v>
       </c>
       <c r="P12" s="1"/>
-      <c r="S12" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T12" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U12" s="43">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V12" s="43">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="S12" s="46">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="T12" s="46">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="U12" s="46">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="V12" s="46">
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
@@ -32842,19 +32516,19 @@
         <v>10.5</v>
       </c>
       <c r="P13" s="1"/>
-      <c r="S13" s="43">
+      <c r="S13" s="46">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="T13" s="43">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="U13" s="43">
+      <c r="T13" s="46">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="U13" s="46">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="V13" s="43">
+      <c r="V13" s="46">
         <f t="shared" si="3"/>
         <v>10.5</v>
       </c>
@@ -32899,19 +32573,19 @@
         <v>18.5</v>
       </c>
       <c r="P14" s="1"/>
-      <c r="S14" s="43">
+      <c r="S14" s="46">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T14" s="43">
+      <c r="T14" s="46">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U14" s="43">
+      <c r="U14" s="46">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="V14" s="43">
+      <c r="V14" s="46">
         <f t="shared" si="3"/>
         <v>18.5</v>
       </c>
@@ -32928,12 +32602,24 @@
       <c r="C15" s="27" t="b">
         <v>0</v>
       </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+      <c r="D15" s="1">
+        <v>2</v>
+      </c>
+      <c r="E15" s="1">
+        <v>2</v>
+      </c>
+      <c r="F15" s="1">
+        <v>2</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2</v>
+      </c>
+      <c r="H15" s="1">
+        <v>6</v>
+      </c>
+      <c r="I15" s="1">
+        <v>6</v>
+      </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -32944,21 +32630,21 @@
         <v>0</v>
       </c>
       <c r="P15" s="1"/>
-      <c r="S15" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T15" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="43">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="43">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="S15" s="46">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="T15" s="46">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="U15" s="46">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="V15" s="46">
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
@@ -33001,19 +32687,19 @@
         <v>10.5</v>
       </c>
       <c r="P16" s="1"/>
-      <c r="S16" s="43">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="T16" s="43">
+      <c r="S16" s="46">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="T16" s="46">
         <f t="shared" si="1"/>
         <v>4.5</v>
       </c>
-      <c r="U16" s="43">
+      <c r="U16" s="46">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="V16" s="43">
+      <c r="V16" s="46">
         <f t="shared" si="3"/>
         <v>10.5</v>
       </c>
@@ -33058,19 +32744,19 @@
         <v>15</v>
       </c>
       <c r="P17" s="1"/>
-      <c r="S17" s="43">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="T17" s="43">
+      <c r="S17" s="46">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="T17" s="46">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="U17" s="43">
+      <c r="U17" s="46">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="V17" s="43">
+      <c r="V17" s="46">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
@@ -33115,19 +32801,19 @@
         <v>17.5</v>
       </c>
       <c r="P18" s="1"/>
-      <c r="S18" s="43">
+      <c r="S18" s="46">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="T18" s="43">
+      <c r="T18" s="46">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="U18" s="43">
+      <c r="U18" s="46">
         <f t="shared" si="2"/>
         <v>7.5</v>
       </c>
-      <c r="V18" s="43">
+      <c r="V18" s="46">
         <f t="shared" si="3"/>
         <v>17.5</v>
       </c>
@@ -33172,19 +32858,19 @@
         <v>14</v>
       </c>
       <c r="P19" s="1"/>
-      <c r="S19" s="43">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="T19" s="43">
+      <c r="S19" s="46">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="T19" s="46">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="U19" s="43">
+      <c r="U19" s="46">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="V19" s="43">
+      <c r="V19" s="46">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
@@ -33229,19 +32915,19 @@
         <v>14.5</v>
       </c>
       <c r="P20" s="1"/>
-      <c r="S20" s="43">
+      <c r="S20" s="46">
         <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
-      <c r="T20" s="43">
+      <c r="T20" s="46">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="U20" s="43">
+      <c r="U20" s="46">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V20" s="43">
+      <c r="V20" s="46">
         <f t="shared" si="3"/>
         <v>14.5</v>
       </c>
@@ -33286,19 +32972,19 @@
         <v>6</v>
       </c>
       <c r="P21" s="1"/>
-      <c r="S21" s="43">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="T21" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U21" s="43">
+      <c r="S21" s="46">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="T21" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="46">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="V21" s="43">
+      <c r="V21" s="46">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
@@ -33315,12 +33001,24 @@
       <c r="C22" s="27" t="b">
         <v>0</v>
       </c>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
+      <c r="D22" s="1">
+        <v>2</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2</v>
+      </c>
+      <c r="F22" s="1">
+        <v>2</v>
+      </c>
+      <c r="G22" s="1">
+        <v>2</v>
+      </c>
+      <c r="H22" s="1">
+        <v>6</v>
+      </c>
+      <c r="I22" s="1">
+        <v>6</v>
+      </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -33331,21 +33029,21 @@
         <v>0</v>
       </c>
       <c r="P22" s="1"/>
-      <c r="S22" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T22" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U22" s="43">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V22" s="43">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="S22" s="46">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="T22" s="46">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="U22" s="46">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="V22" s="46">
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
@@ -33388,19 +33086,19 @@
         <v>18</v>
       </c>
       <c r="P23" s="1"/>
-      <c r="S23" s="43">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="T23" s="43">
+      <c r="S23" s="46">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="T23" s="46">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="U23" s="43">
+      <c r="U23" s="46">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V23" s="43">
+      <c r="V23" s="46">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
@@ -33445,19 +33143,19 @@
         <v>13</v>
       </c>
       <c r="P24" s="1"/>
-      <c r="S24" s="43">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="T24" s="43">
+      <c r="S24" s="46">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="T24" s="46">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U24" s="43">
+      <c r="U24" s="46">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="V24" s="43">
+      <c r="V24" s="46">
         <f t="shared" si="3"/>
         <v>13</v>
       </c>
@@ -33502,19 +33200,19 @@
         <v>12.5</v>
       </c>
       <c r="P25" s="1"/>
-      <c r="S25" s="43">
+      <c r="S25" s="46">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T25" s="43">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="U25" s="43">
+      <c r="T25" s="46">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="U25" s="46">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="V25" s="43">
+      <c r="V25" s="46">
         <f t="shared" si="3"/>
         <v>12.5</v>
       </c>
@@ -33559,19 +33257,19 @@
         <v>19.5</v>
       </c>
       <c r="P26" s="1"/>
-      <c r="S26" s="43">
+      <c r="S26" s="46">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T26" s="43">
+      <c r="T26" s="46">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U26" s="43">
+      <c r="U26" s="46">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V26" s="43">
+      <c r="V26" s="46">
         <f t="shared" si="3"/>
         <v>19.5</v>
       </c>
@@ -33616,19 +33314,19 @@
         <v>19.5</v>
       </c>
       <c r="P27" s="1"/>
-      <c r="S27" s="43">
+      <c r="S27" s="46">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T27" s="43">
+      <c r="T27" s="46">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U27" s="43">
+      <c r="U27" s="46">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V27" s="43">
+      <c r="V27" s="46">
         <f t="shared" si="3"/>
         <v>19.5</v>
       </c>
@@ -33673,19 +33371,19 @@
         <v>6</v>
       </c>
       <c r="P28" s="1"/>
-      <c r="S28" s="43">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="T28" s="43">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="U28" s="43">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="V28" s="43">
+      <c r="S28" s="46">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="T28" s="46">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="U28" s="46">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="V28" s="46">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
@@ -33702,12 +33400,24 @@
       <c r="C29" s="27" t="b">
         <v>0</v>
       </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+      <c r="D29" s="1">
+        <v>2</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2</v>
+      </c>
+      <c r="F29" s="1">
+        <v>2</v>
+      </c>
+      <c r="G29" s="1">
+        <v>2</v>
+      </c>
+      <c r="H29" s="1">
+        <v>6</v>
+      </c>
+      <c r="I29" s="1">
+        <v>6</v>
+      </c>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -33718,21 +33428,21 @@
         <v>0</v>
       </c>
       <c r="P29" s="1"/>
-      <c r="S29" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T29" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U29" s="43">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V29" s="43">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="S29" s="46">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="T29" s="46">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="U29" s="46">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="V29" s="46">
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.25">
@@ -33775,19 +33485,19 @@
         <v>12</v>
       </c>
       <c r="P30" s="1"/>
-      <c r="S30" s="43">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="T30" s="43">
+      <c r="S30" s="46">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="T30" s="46">
         <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="U30" s="43">
+      <c r="U30" s="46">
         <f t="shared" si="2"/>
         <v>7.5</v>
       </c>
-      <c r="V30" s="43">
+      <c r="V30" s="46">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
@@ -33832,19 +33542,19 @@
         <v>11</v>
       </c>
       <c r="P31" s="1"/>
-      <c r="S31" s="43">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="T31" s="43">
+      <c r="S31" s="46">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="T31" s="46">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U31" s="43">
+      <c r="U31" s="46">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="V31" s="43">
+      <c r="V31" s="46">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
@@ -33889,19 +33599,19 @@
         <v>18</v>
       </c>
       <c r="P32" s="1"/>
-      <c r="S32" s="43">
+      <c r="S32" s="46">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="T32" s="43">
+      <c r="T32" s="46">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="U32" s="43">
+      <c r="U32" s="46">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V32" s="43">
+      <c r="V32" s="46">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
@@ -33946,19 +33656,19 @@
         <v>15.5</v>
       </c>
       <c r="P33" s="1"/>
-      <c r="S33" s="43">
+      <c r="S33" s="46">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T33" s="43">
+      <c r="T33" s="46">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U33" s="43">
+      <c r="U33" s="46">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V33" s="43">
+      <c r="V33" s="46">
         <f t="shared" si="3"/>
         <v>15.5</v>
       </c>
@@ -34003,19 +33713,19 @@
         <v>17.5</v>
       </c>
       <c r="P34" s="1"/>
-      <c r="S34" s="43">
+      <c r="S34" s="46">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="T34" s="43">
+      <c r="T34" s="46">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U34" s="43">
+      <c r="U34" s="46">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="V34" s="43">
+      <c r="V34" s="46">
         <f t="shared" si="3"/>
         <v>17.5</v>
       </c>
@@ -34060,19 +33770,19 @@
         <v>14</v>
       </c>
       <c r="P35" s="1"/>
-      <c r="S35" s="43">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="T35" s="43">
+      <c r="S35" s="46">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="T35" s="46">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U35" s="43">
+      <c r="U35" s="46">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="V35" s="43">
+      <c r="V35" s="46">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
@@ -34117,19 +33827,19 @@
         <v>19</v>
       </c>
       <c r="P36" s="1"/>
-      <c r="S36" s="43">
+      <c r="S36" s="46">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="T36" s="43">
+      <c r="T36" s="46">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="U36" s="43">
+      <c r="U36" s="46">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V36" s="43">
+      <c r="V36" s="46">
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
@@ -34174,19 +33884,19 @@
         <v>18.5</v>
       </c>
       <c r="P37" s="1"/>
-      <c r="S37" s="43">
+      <c r="S37" s="46">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T37" s="43">
+      <c r="T37" s="46">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U37" s="43">
+      <c r="U37" s="46">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="V37" s="43">
+      <c r="V37" s="46">
         <f t="shared" si="3"/>
         <v>18.5</v>
       </c>
@@ -34231,19 +33941,19 @@
         <v>18</v>
       </c>
       <c r="P38" s="1"/>
-      <c r="S38" s="43">
+      <c r="S38" s="46">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="T38" s="43">
+      <c r="T38" s="46">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="U38" s="43">
+      <c r="U38" s="46">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V38" s="43">
+      <c r="V38" s="46">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
@@ -34288,19 +33998,19 @@
         <v>11.5</v>
       </c>
       <c r="P39" s="1"/>
-      <c r="S39" s="43">
+      <c r="S39" s="46">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="T39" s="43">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="U39" s="43">
+      <c r="T39" s="46">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="U39" s="46">
         <f t="shared" si="2"/>
         <v>5.5</v>
       </c>
-      <c r="V39" s="43">
+      <c r="V39" s="46">
         <f t="shared" si="3"/>
         <v>11.5</v>
       </c>
@@ -34345,19 +34055,19 @@
         <v>13.5</v>
       </c>
       <c r="P40" s="1"/>
-      <c r="S40" s="43">
+      <c r="S40" s="46">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T40" s="43">
+      <c r="T40" s="46">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U40" s="43">
+      <c r="U40" s="46">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="V40" s="43">
+      <c r="V40" s="46">
         <f t="shared" si="3"/>
         <v>13.5</v>
       </c>
@@ -34402,19 +34112,19 @@
         <v>6.5</v>
       </c>
       <c r="P41" s="1"/>
-      <c r="S41" s="43">
+      <c r="S41" s="46">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="T41" s="43">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="U41" s="43">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="V41" s="43">
+      <c r="T41" s="46">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="U41" s="46">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="V41" s="46">
         <f t="shared" si="3"/>
         <v>6.5</v>
       </c>
@@ -34431,12 +34141,24 @@
       <c r="C42" s="27" t="b">
         <v>0</v>
       </c>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
+      <c r="D42" s="1">
+        <v>2</v>
+      </c>
+      <c r="E42" s="1">
+        <v>2</v>
+      </c>
+      <c r="F42" s="1">
+        <v>2</v>
+      </c>
+      <c r="G42" s="1">
+        <v>2</v>
+      </c>
+      <c r="H42" s="1">
+        <v>6</v>
+      </c>
+      <c r="I42" s="1">
+        <v>6</v>
+      </c>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
@@ -34447,21 +34169,21 @@
         <v>0</v>
       </c>
       <c r="P42" s="1"/>
-      <c r="S42" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T42" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U42" s="43">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V42" s="43">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="S42" s="46">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="T42" s="46">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="U42" s="46">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="V42" s="46">
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.25">
@@ -34504,19 +34226,19 @@
         <v>3</v>
       </c>
       <c r="P43" s="1"/>
-      <c r="S43" s="43">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="T43" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U43" s="43">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="V43" s="43">
+      <c r="S43" s="46">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="T43" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U43" s="46">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="V43" s="46">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
@@ -34533,12 +34255,24 @@
       <c r="C44" s="27" t="b">
         <v>0</v>
       </c>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
+      <c r="D44" s="1">
+        <v>2</v>
+      </c>
+      <c r="E44" s="1">
+        <v>2</v>
+      </c>
+      <c r="F44" s="1">
+        <v>2</v>
+      </c>
+      <c r="G44" s="1">
+        <v>2</v>
+      </c>
+      <c r="H44" s="1">
+        <v>6</v>
+      </c>
+      <c r="I44" s="1">
+        <v>6</v>
+      </c>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
@@ -34549,21 +34283,21 @@
         <v>0</v>
       </c>
       <c r="P44" s="1"/>
-      <c r="S44" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T44" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U44" s="43">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V44" s="43">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="S44" s="46">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="T44" s="46">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="U44" s="46">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="V44" s="46">
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.25">
@@ -34606,19 +34340,19 @@
         <v>14.5</v>
       </c>
       <c r="P45" s="1"/>
-      <c r="S45" s="43">
+      <c r="S45" s="46">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="T45" s="43">
+      <c r="T45" s="46">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U45" s="43">
+      <c r="U45" s="46">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V45" s="43">
+      <c r="V45" s="46">
         <f t="shared" si="3"/>
         <v>14.5</v>
       </c>
@@ -34663,19 +34397,19 @@
         <v>4</v>
       </c>
       <c r="P46" s="1"/>
-      <c r="S46" s="43">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="T46" s="43">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="U46" s="43">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V46" s="43">
+      <c r="S46" s="46">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="T46" s="46">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="U46" s="46">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V46" s="46">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
@@ -34720,19 +34454,19 @@
         <v>14.5</v>
       </c>
       <c r="P47" s="1"/>
-      <c r="S47" s="43">
+      <c r="S47" s="46">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T47" s="43">
+      <c r="T47" s="46">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U47" s="43">
+      <c r="U47" s="46">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="V47" s="43">
+      <c r="V47" s="46">
         <f t="shared" si="3"/>
         <v>14.5</v>
       </c>
@@ -34777,19 +34511,19 @@
         <v>7</v>
       </c>
       <c r="P48" s="1"/>
-      <c r="S48" s="43">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="T48" s="43">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="U48" s="43">
+      <c r="S48" s="46">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="T48" s="46">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="U48" s="46">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="V48" s="43">
+      <c r="V48" s="46">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -34834,19 +34568,19 @@
         <v>14.5</v>
       </c>
       <c r="P49" s="1"/>
-      <c r="S49" s="43">
+      <c r="S49" s="46">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T49" s="43">
+      <c r="T49" s="46">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U49" s="43">
+      <c r="U49" s="46">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="V49" s="43">
+      <c r="V49" s="46">
         <f t="shared" si="3"/>
         <v>14.5</v>
       </c>
@@ -34863,12 +34597,24 @@
       <c r="C50" s="27" t="b">
         <v>0</v>
       </c>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
+      <c r="D50" s="1">
+        <v>2</v>
+      </c>
+      <c r="E50" s="1">
+        <v>2</v>
+      </c>
+      <c r="F50" s="1">
+        <v>2</v>
+      </c>
+      <c r="G50" s="1">
+        <v>2</v>
+      </c>
+      <c r="H50" s="1">
+        <v>6</v>
+      </c>
+      <c r="I50" s="1">
+        <v>6</v>
+      </c>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
@@ -34879,21 +34625,21 @@
         <v>0</v>
       </c>
       <c r="P50" s="1"/>
-      <c r="S50" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T50" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U50" s="43">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V50" s="43">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="S50" s="46">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="T50" s="46">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="U50" s="46">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="V50" s="46">
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.25">
@@ -34936,19 +34682,19 @@
         <v>19.5</v>
       </c>
       <c r="P51" s="1"/>
-      <c r="S51" s="43">
+      <c r="S51" s="46">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T51" s="43">
+      <c r="T51" s="46">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U51" s="43">
+      <c r="U51" s="46">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V51" s="43">
+      <c r="V51" s="46">
         <f t="shared" si="3"/>
         <v>19.5</v>
       </c>
@@ -34993,19 +34739,19 @@
         <v>17</v>
       </c>
       <c r="P52" s="1"/>
-      <c r="S52" s="43">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="T52" s="43">
+      <c r="S52" s="46">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="T52" s="46">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="U52" s="43">
+      <c r="U52" s="46">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="V52" s="43">
+      <c r="V52" s="46">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
@@ -35022,12 +34768,24 @@
       <c r="C53" s="27" t="b">
         <v>0</v>
       </c>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
+      <c r="D53" s="1">
+        <v>2</v>
+      </c>
+      <c r="E53" s="1">
+        <v>2</v>
+      </c>
+      <c r="F53" s="1">
+        <v>2</v>
+      </c>
+      <c r="G53" s="1">
+        <v>2</v>
+      </c>
+      <c r="H53" s="1">
+        <v>6</v>
+      </c>
+      <c r="I53" s="1">
+        <v>6</v>
+      </c>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
@@ -35038,21 +34796,21 @@
         <v>0</v>
       </c>
       <c r="P53" s="1"/>
-      <c r="S53" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T53" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U53" s="43">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V53" s="43">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="S53" s="46">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="T53" s="46">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="U53" s="46">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="V53" s="46">
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -35095,19 +34853,19 @@
         <v>18</v>
       </c>
       <c r="P54" s="1"/>
-      <c r="S54" s="43">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="T54" s="43">
+      <c r="S54" s="46">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="T54" s="46">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="U54" s="43">
+      <c r="U54" s="46">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V54" s="43">
+      <c r="V54" s="46">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
@@ -35152,19 +34910,19 @@
         <v>19.5</v>
       </c>
       <c r="P55" s="1"/>
-      <c r="S55" s="43">
+      <c r="S55" s="46">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T55" s="43">
+      <c r="T55" s="46">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U55" s="43">
+      <c r="U55" s="46">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V55" s="43">
+      <c r="V55" s="46">
         <f t="shared" si="3"/>
         <v>19.5</v>
       </c>
@@ -35209,19 +34967,19 @@
         <v>13</v>
       </c>
       <c r="P56" s="1"/>
-      <c r="S56" s="43">
+      <c r="S56" s="46">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="T56" s="43">
+      <c r="T56" s="46">
         <f t="shared" si="1"/>
         <v>3.5</v>
       </c>
-      <c r="U56" s="43">
+      <c r="U56" s="46">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="V56" s="43">
+      <c r="V56" s="46">
         <f t="shared" si="3"/>
         <v>13</v>
       </c>
@@ -35238,12 +34996,24 @@
       <c r="C57" s="27" t="b">
         <v>0</v>
       </c>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
+      <c r="D57" s="1">
+        <v>2</v>
+      </c>
+      <c r="E57" s="1">
+        <v>2</v>
+      </c>
+      <c r="F57" s="1">
+        <v>2</v>
+      </c>
+      <c r="G57" s="1">
+        <v>2</v>
+      </c>
+      <c r="H57" s="1">
+        <v>6</v>
+      </c>
+      <c r="I57" s="1">
+        <v>6</v>
+      </c>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
@@ -35254,21 +35024,21 @@
         <v>0</v>
       </c>
       <c r="P57" s="1"/>
-      <c r="S57" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T57" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U57" s="43">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V57" s="43">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="S57" s="46">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="T57" s="46">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="U57" s="46">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="V57" s="46">
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.25">
@@ -35283,12 +35053,24 @@
       <c r="C58" s="27" t="b">
         <v>0</v>
       </c>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
+      <c r="D58" s="1">
+        <v>2</v>
+      </c>
+      <c r="E58" s="1">
+        <v>2</v>
+      </c>
+      <c r="F58" s="1">
+        <v>2</v>
+      </c>
+      <c r="G58" s="1">
+        <v>2</v>
+      </c>
+      <c r="H58" s="1">
+        <v>6</v>
+      </c>
+      <c r="I58" s="1">
+        <v>6</v>
+      </c>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
@@ -35299,21 +35081,21 @@
         <v>0</v>
       </c>
       <c r="P58" s="1"/>
-      <c r="S58" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T58" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U58" s="43">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V58" s="43">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="S58" s="46">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="T58" s="46">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="U58" s="46">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="V58" s="46">
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.25">
@@ -35356,19 +35138,19 @@
         <v>14.5</v>
       </c>
       <c r="P59" s="1"/>
-      <c r="S59" s="43">
+      <c r="S59" s="46">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T59" s="43">
+      <c r="T59" s="46">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U59" s="43">
+      <c r="U59" s="46">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="V59" s="43">
+      <c r="V59" s="46">
         <f t="shared" si="3"/>
         <v>14.5</v>
       </c>
@@ -35413,19 +35195,19 @@
         <v>14.5</v>
       </c>
       <c r="P60" s="1"/>
-      <c r="S60" s="43">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="T60" s="43">
+      <c r="S60" s="46">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="T60" s="46">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U60" s="43">
+      <c r="U60" s="46">
         <f t="shared" si="2"/>
         <v>7.5</v>
       </c>
-      <c r="V60" s="43">
+      <c r="V60" s="46">
         <f t="shared" si="3"/>
         <v>14.5</v>
       </c>
@@ -35470,19 +35252,19 @@
         <v>15.5</v>
       </c>
       <c r="P61" s="1"/>
-      <c r="S61" s="43">
+      <c r="S61" s="46">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T61" s="43">
+      <c r="T61" s="46">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="U61" s="43">
+      <c r="U61" s="46">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="V61" s="43">
+      <c r="V61" s="46">
         <f t="shared" si="3"/>
         <v>15.5</v>
       </c>
@@ -35527,19 +35309,19 @@
         <v>15.5</v>
       </c>
       <c r="P62" s="1"/>
-      <c r="S62" s="43">
+      <c r="S62" s="46">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T62" s="43">
+      <c r="T62" s="46">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U62" s="43">
+      <c r="U62" s="46">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V62" s="43">
+      <c r="V62" s="46">
         <f t="shared" si="3"/>
         <v>15.5</v>
       </c>
@@ -35584,19 +35366,19 @@
         <v>17.5</v>
       </c>
       <c r="P63" s="1"/>
-      <c r="S63" s="43">
+      <c r="S63" s="46">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T63" s="43">
+      <c r="T63" s="46">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="U63" s="43">
+      <c r="U63" s="46">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V63" s="43">
+      <c r="V63" s="46">
         <f t="shared" si="3"/>
         <v>17.5</v>
       </c>
@@ -35641,19 +35423,19 @@
         <v>15</v>
       </c>
       <c r="P64" s="1"/>
-      <c r="S64" s="43">
+      <c r="S64" s="46">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="T64" s="43">
+      <c r="T64" s="46">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U64" s="43">
+      <c r="U64" s="46">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="V64" s="43">
+      <c r="V64" s="46">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
@@ -35675,25 +35457,25 @@
       <c r="N65" s="1"/>
       <c r="O65" s="1"/>
       <c r="P65" s="1"/>
-      <c r="S65" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T65" s="43">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U65" s="43">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V65" s="43">
+      <c r="S65" s="46">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T65" s="46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U65" s="46">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V65" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:C64" xr:uid="{0F3EC6E4-73FE-451F-9DA1-2F8671C4541C}"/>
+  <autoFilter ref="A4:B64" xr:uid="{0F3EC6E4-73FE-451F-9DA1-2F8671C4541C}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>

--- a/resources/Marks/2026/even/Physics For Computer Engineers.xlsx
+++ b/resources/Marks/2026/even/Physics For Computer Engineers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gusindia01-my.sharepoint.com/personal/nitesh_kumar_ddn_upes_ac_in/Documents/UPES/2026/Jan-May-2026/Physics for Computer Engineers B77 B78/Marks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3578" documentId="11_3FC952BF37FB7C428065D6D94F732ED04C5A5A3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2430891F-A738-483A-AA82-FF0CCB144A0F}"/>
+  <xr:revisionPtr revIDLastSave="3583" documentId="11_3FC952BF37FB7C428065D6D94F732ED04C5A5A3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4573DBF6-F359-46BD-BA4D-68B9AF8EEA6B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="553" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,9 +22,9 @@
     <sheet name="Assignment 1" sheetId="6" r:id="rId7"/>
     <sheet name="Assignment 2" sheetId="9" r:id="rId8"/>
     <sheet name="Class Test 2" sheetId="8" r:id="rId9"/>
-    <sheet name="Remedial Class" sheetId="15" r:id="rId10"/>
-    <sheet name="Sheet2" sheetId="11" state="hidden" r:id="rId11"/>
-    <sheet name="Sheet3" sheetId="12" state="hidden" r:id="rId12"/>
+    <sheet name="Sheet2" sheetId="11" state="hidden" r:id="rId10"/>
+    <sheet name="Sheet3" sheetId="12" state="hidden" r:id="rId11"/>
+    <sheet name="Lab Marks " sheetId="16" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Class Test 2'!$A$4:$B$64</definedName>
@@ -87,9 +87,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="175">
   <si>
     <t>Final Marks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physics for Computer Engineers (PHYS 1036) </t>
   </si>
   <si>
     <t xml:space="preserve">Name </t>
@@ -101,19 +104,34 @@
     <t>Batch</t>
   </si>
   <si>
+    <t>Quiz 1</t>
+  </si>
+  <si>
     <t>Assignment 1</t>
   </si>
   <si>
-    <t>Assignment 2</t>
+    <t>Class Test 1</t>
   </si>
   <si>
-    <t>Class Test 1</t>
+    <t>Quiz 2</t>
+  </si>
+  <si>
+    <t>Assignment 2</t>
   </si>
   <si>
     <t>Class Test 2</t>
   </si>
   <si>
     <t>IA</t>
+  </si>
+  <si>
+    <t>Lab</t>
+  </si>
+  <si>
+    <t>CIA</t>
+  </si>
+  <si>
+    <t>CIA_Weightage</t>
   </si>
   <si>
     <t>Mid Sem</t>
@@ -491,7 +509,13 @@
     <t>vinit.29353@stu.upes.ac.in</t>
   </si>
   <si>
-    <t>Mid Sem Examination</t>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Median</t>
   </si>
   <si>
     <t>CO1</t>
@@ -500,13 +524,10 @@
     <t>CO2</t>
   </si>
   <si>
-    <t>CO3</t>
+    <t>Student Id</t>
   </si>
   <si>
     <t>Name</t>
-  </si>
-  <si>
-    <t>Student ID</t>
   </si>
   <si>
     <t>Q1</t>
@@ -542,13 +563,28 @@
     <t>Q11</t>
   </si>
   <si>
+    <t>P/A</t>
+  </si>
+  <si>
+    <t>Mid Sem Examination</t>
+  </si>
+  <si>
+    <t>CO2/CO1</t>
+  </si>
+  <si>
+    <t>Student ID</t>
+  </si>
+  <si>
     <t>End Sem Examination</t>
+  </si>
+  <si>
+    <t>CO3</t>
   </si>
   <si>
     <t>CO4</t>
   </si>
   <si>
-    <t>Student Id</t>
+    <t>CO5</t>
   </si>
   <si>
     <t>Email</t>
@@ -575,53 +611,14 @@
     <t>Group</t>
   </si>
   <si>
-    <t>Quiz 1</t>
-  </si>
-  <si>
-    <t>Quiz 2</t>
-  </si>
-  <si>
-    <t>Lab</t>
-  </si>
-  <si>
-    <t>CIA</t>
-  </si>
-  <si>
-    <t>CIA_Weightage</t>
-  </si>
-  <si>
-    <t>P/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Physics for Computer Engineers (PHYS 1036) </t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Median</t>
-  </si>
-  <si>
-    <t>CO2/CO1</t>
-  </si>
-  <si>
-    <t>Remedial Class Attendance (Batch 77/78) Jan-June 2026</t>
-  </si>
-  <si>
-    <t>CO5</t>
-  </si>
-  <si>
-    <t>SN</t>
+    <t>Lab Marks</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -677,13 +674,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -808,7 +798,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -929,15 +919,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -946,9 +927,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1114,6 +1092,10 @@
     </a>
   </bag>
 </FeaturePropertyBags>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1549,122 +1531,122 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47"/>
-      <c r="S1" s="47"/>
+      <c r="A1" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
       <c r="T1" s="24"/>
     </row>
     <row r="2" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="47" t="s">
-        <v>168</v>
-      </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
+      <c r="A2" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="44"/>
       <c r="T2" s="25"/>
     </row>
     <row r="3" spans="1:22" s="22" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="37" t="s">
-        <v>162</v>
+        <v>5</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F3" s="37" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G3" s="37" t="s">
-        <v>163</v>
+        <v>8</v>
       </c>
       <c r="H3" s="37" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I3" s="37" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J3" s="37" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K3" s="37" t="s">
-        <v>164</v>
+        <v>12</v>
       </c>
       <c r="L3" s="37" t="s">
-        <v>165</v>
+        <v>13</v>
       </c>
       <c r="M3" s="41" t="s">
-        <v>166</v>
+        <v>14</v>
       </c>
       <c r="N3" s="37" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="O3" s="37" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P3" s="37" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Q3" s="37" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R3" s="37" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="S3" s="37" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="U3" s="42" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="V3" s="23" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="8" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="14">
@@ -1726,7 +1708,7 @@
     </row>
     <row r="5" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B5" s="10">
         <v>590029213</v>
@@ -1795,7 +1777,7 @@
       </c>
       <c r="S5" s="39"/>
       <c r="U5" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="V5">
         <v>122507103</v>
@@ -1803,7 +1785,7 @@
     </row>
     <row r="6" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B6" s="10">
         <v>590029270</v>
@@ -1872,7 +1854,7 @@
       </c>
       <c r="S6" s="39"/>
       <c r="U6" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="V6">
         <v>25010104938</v>
@@ -1880,7 +1862,7 @@
     </row>
     <row r="7" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B7" s="10">
         <v>590029204</v>
@@ -1949,7 +1931,7 @@
       </c>
       <c r="S7" s="39"/>
       <c r="U7" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="V7">
         <v>25010104918</v>
@@ -1957,7 +1939,7 @@
     </row>
     <row r="8" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B8" s="10">
         <v>590029109</v>
@@ -2026,7 +2008,7 @@
       </c>
       <c r="S8" s="39"/>
       <c r="U8" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="V8">
         <v>25010104943</v>
@@ -2034,7 +2016,7 @@
     </row>
     <row r="9" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B9" s="10">
         <v>590029070</v>
@@ -2103,7 +2085,7 @@
       </c>
       <c r="S9" s="39"/>
       <c r="U9" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="V9">
         <v>25010104926</v>
@@ -2111,7 +2093,7 @@
     </row>
     <row r="10" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B10" s="10">
         <v>590029157</v>
@@ -2180,7 +2162,7 @@
       </c>
       <c r="S10" s="39"/>
       <c r="U10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="V10">
         <v>25010104890</v>
@@ -2188,7 +2170,7 @@
     </row>
     <row r="11" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B11" s="10">
         <v>590027157</v>
@@ -2257,7 +2239,7 @@
       </c>
       <c r="S11" s="39"/>
       <c r="U11" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="V11">
         <v>25010104880</v>
@@ -2265,7 +2247,7 @@
     </row>
     <row r="12" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B12" s="10">
         <v>590029274</v>
@@ -2334,7 +2316,7 @@
       </c>
       <c r="S12" s="39"/>
       <c r="U12" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="V12">
         <v>25010104928</v>
@@ -2342,7 +2324,7 @@
     </row>
     <row r="13" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B13" s="10">
         <v>590028572</v>
@@ -2411,7 +2393,7 @@
       </c>
       <c r="S13" s="39"/>
       <c r="U13" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="V13">
         <v>25010104903</v>
@@ -2419,7 +2401,7 @@
     </row>
     <row r="14" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B14" s="10">
         <v>590029230</v>
@@ -2488,7 +2470,7 @@
       </c>
       <c r="S14" s="39"/>
       <c r="U14" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="V14">
         <v>25010104910</v>
@@ -2496,7 +2478,7 @@
     </row>
     <row r="15" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B15" s="10">
         <v>590029169</v>
@@ -2565,7 +2547,7 @@
       </c>
       <c r="S15" s="39"/>
       <c r="U15" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="V15">
         <v>25010104944</v>
@@ -2573,7 +2555,7 @@
     </row>
     <row r="16" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B16" s="10">
         <v>590029112</v>
@@ -2642,7 +2624,7 @@
       </c>
       <c r="S16" s="39"/>
       <c r="U16" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="V16">
         <v>25010104876</v>
@@ -2650,7 +2632,7 @@
     </row>
     <row r="17" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B17" s="10">
         <v>590025556</v>
@@ -2719,7 +2701,7 @@
       </c>
       <c r="S17" s="39"/>
       <c r="U17" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="V17">
         <v>122515743</v>
@@ -2727,7 +2709,7 @@
     </row>
     <row r="18" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B18" s="10">
         <v>590027830</v>
@@ -2796,7 +2778,7 @@
       </c>
       <c r="S18" s="1"/>
       <c r="U18" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="V18">
         <v>25010104886</v>
@@ -2804,7 +2786,7 @@
     </row>
     <row r="19" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B19" s="10">
         <v>590028360</v>
@@ -2873,7 +2855,7 @@
       </c>
       <c r="S19" s="1"/>
       <c r="U19" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="V19">
         <v>25010104881</v>
@@ -2881,7 +2863,7 @@
     </row>
     <row r="20" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B20" s="10">
         <v>590029237</v>
@@ -2950,7 +2932,7 @@
       </c>
       <c r="S20" s="1"/>
       <c r="U20" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="V20">
         <v>25010104909</v>
@@ -2958,7 +2940,7 @@
     </row>
     <row r="21" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B21" s="10">
         <v>590029079</v>
@@ -3027,7 +3009,7 @@
       </c>
       <c r="S21" s="1"/>
       <c r="U21" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="V21">
         <v>25010104906</v>
@@ -3035,7 +3017,7 @@
     </row>
     <row r="22" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B22" s="10">
         <v>590029145</v>
@@ -3104,7 +3086,7 @@
       </c>
       <c r="S22" s="1"/>
       <c r="U22" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="V22">
         <v>25010104892</v>
@@ -3112,7 +3094,7 @@
     </row>
     <row r="23" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B23" s="10">
         <v>590029209</v>
@@ -3181,7 +3163,7 @@
       </c>
       <c r="S23" s="1"/>
       <c r="U23" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="V23">
         <v>25010104887</v>
@@ -3189,7 +3171,7 @@
     </row>
     <row r="24" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B24" s="10">
         <v>590027268</v>
@@ -3258,7 +3240,7 @@
       </c>
       <c r="S24" s="36"/>
       <c r="U24" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V24">
         <v>25010104933</v>
@@ -3266,7 +3248,7 @@
     </row>
     <row r="25" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B25" s="10">
         <v>590029227</v>
@@ -3335,7 +3317,7 @@
       </c>
       <c r="S25" s="36"/>
       <c r="U25" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="V25">
         <v>25010104900</v>
@@ -3343,7 +3325,7 @@
     </row>
     <row r="26" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B26" s="10">
         <v>590029241</v>
@@ -3412,7 +3394,7 @@
       </c>
       <c r="S26" s="36"/>
       <c r="U26" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="V26">
         <v>25010104915</v>
@@ -3420,7 +3402,7 @@
     </row>
     <row r="27" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B27" s="10">
         <v>590023855</v>
@@ -3489,7 +3471,7 @@
       </c>
       <c r="S27" s="36"/>
       <c r="U27" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="V27">
         <v>25010104868</v>
@@ -3497,7 +3479,7 @@
     </row>
     <row r="28" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B28" s="10">
         <v>590029215</v>
@@ -3566,7 +3548,7 @@
       </c>
       <c r="S28" s="36"/>
       <c r="U28" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="V28">
         <v>25010104884</v>
@@ -3574,7 +3556,7 @@
     </row>
     <row r="29" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B29" s="10">
         <v>590029111</v>
@@ -3643,7 +3625,7 @@
       </c>
       <c r="S29" s="36"/>
       <c r="U29" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="V29">
         <v>25010104888</v>
@@ -3651,7 +3633,7 @@
     </row>
     <row r="30" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B30" s="10">
         <v>590028683</v>
@@ -3720,7 +3702,7 @@
       </c>
       <c r="S30" s="36"/>
       <c r="U30" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="V30">
         <v>25010104936</v>
@@ -3728,7 +3710,7 @@
     </row>
     <row r="31" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B31" s="10">
         <v>590029121</v>
@@ -3797,7 +3779,7 @@
       </c>
       <c r="S31" s="36"/>
       <c r="U31" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="V31">
         <v>25010104875</v>
@@ -3805,7 +3787,7 @@
     </row>
     <row r="32" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B32" s="10">
         <v>590029048</v>
@@ -3874,7 +3856,7 @@
       </c>
       <c r="S32" s="36"/>
       <c r="U32" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="V32">
         <v>25010104925</v>
@@ -3882,7 +3864,7 @@
     </row>
     <row r="33" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B33" s="10">
         <v>590029184</v>
@@ -3951,7 +3933,7 @@
       </c>
       <c r="S33" s="36"/>
       <c r="U33" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="V33">
         <v>25010104879</v>
@@ -3959,7 +3941,7 @@
     </row>
     <row r="34" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B34" s="10">
         <v>590029330</v>
@@ -4028,7 +4010,7 @@
       </c>
       <c r="S34" s="36"/>
       <c r="U34" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="V34">
         <v>25010104997</v>
@@ -4036,7 +4018,7 @@
     </row>
     <row r="35" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B35" s="10">
         <v>590027630</v>
@@ -4105,7 +4087,7 @@
       </c>
       <c r="S35" s="36"/>
       <c r="U35" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="V35">
         <v>25010105001</v>
@@ -4113,7 +4095,7 @@
     </row>
     <row r="36" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B36" s="10">
         <v>590029219</v>
@@ -4182,7 +4164,7 @@
       </c>
       <c r="S36" s="36"/>
       <c r="U36" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="V36">
         <v>25010104956</v>
@@ -4190,7 +4172,7 @@
     </row>
     <row r="37" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B37" s="10">
         <v>590028933</v>
@@ -4259,7 +4241,7 @@
       </c>
       <c r="S37" s="36"/>
       <c r="U37" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="V37">
         <v>25010104948</v>
@@ -4267,7 +4249,7 @@
     </row>
     <row r="38" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B38" s="10">
         <v>590027859</v>
@@ -4336,7 +4318,7 @@
       </c>
       <c r="S38" s="1"/>
       <c r="U38" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="V38">
         <v>25010104974</v>
@@ -4344,7 +4326,7 @@
     </row>
     <row r="39" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B39" s="10">
         <v>590028682</v>
@@ -4413,7 +4395,7 @@
       </c>
       <c r="S39" s="1"/>
       <c r="U39" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="V39">
         <v>25010104995</v>
@@ -4421,7 +4403,7 @@
     </row>
     <row r="40" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B40" s="10">
         <v>590023917</v>
@@ -4490,7 +4472,7 @@
       </c>
       <c r="S40" s="1"/>
       <c r="U40" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="V40">
         <v>25010105012</v>
@@ -4498,7 +4480,7 @@
     </row>
     <row r="41" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B41" s="10">
         <v>590023785</v>
@@ -4567,7 +4549,7 @@
       </c>
       <c r="S41" s="1"/>
       <c r="U41" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="V41">
         <v>25010104947</v>
@@ -4575,7 +4557,7 @@
     </row>
     <row r="42" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B42" s="10">
         <v>590029264</v>
@@ -4644,7 +4626,7 @@
       </c>
       <c r="S42" s="1"/>
       <c r="U42" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="V42">
         <v>25010104986</v>
@@ -4652,7 +4634,7 @@
     </row>
     <row r="43" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B43" s="10">
         <v>590029042</v>
@@ -4721,7 +4703,7 @@
       </c>
       <c r="S43" s="1"/>
       <c r="U43" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="V43">
         <v>25010104982</v>
@@ -4729,7 +4711,7 @@
     </row>
     <row r="44" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B44" s="10">
         <v>590029336</v>
@@ -4798,7 +4780,7 @@
       </c>
       <c r="S44" s="1"/>
       <c r="U44" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="V44">
         <v>25010104998</v>
@@ -4806,7 +4788,7 @@
     </row>
     <row r="45" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B45" s="10">
         <v>590029233</v>
@@ -4875,7 +4857,7 @@
       </c>
       <c r="S45" s="1"/>
       <c r="U45" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="V45">
         <v>25010104996</v>
@@ -4883,7 +4865,7 @@
     </row>
     <row r="46" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B46" s="10">
         <v>590029328</v>
@@ -4952,7 +4934,7 @@
       </c>
       <c r="S46" s="1"/>
       <c r="U46" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="V46">
         <v>25010105010</v>
@@ -4960,7 +4942,7 @@
     </row>
     <row r="47" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B47" s="10">
         <v>590028608</v>
@@ -5029,7 +5011,7 @@
       </c>
       <c r="S47" s="1"/>
       <c r="U47" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="V47">
         <v>25010104999</v>
@@ -5037,7 +5019,7 @@
     </row>
     <row r="48" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B48" s="10">
         <v>590028605</v>
@@ -5106,7 +5088,7 @@
       </c>
       <c r="S48" s="1"/>
       <c r="U48" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="V48">
         <v>25010104326</v>
@@ -5114,7 +5096,7 @@
     </row>
     <row r="49" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B49" s="10">
         <v>590026626</v>
@@ -5183,7 +5165,7 @@
       </c>
       <c r="S49" s="1"/>
       <c r="U49" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="V49">
         <v>25010104601</v>
@@ -5191,7 +5173,7 @@
     </row>
     <row r="50" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B50" s="10">
         <v>590029310</v>
@@ -5260,7 +5242,7 @@
       </c>
       <c r="S50" s="1"/>
       <c r="U50" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="V50">
         <v>25010104970</v>
@@ -5268,7 +5250,7 @@
     </row>
     <row r="51" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B51" s="10">
         <v>590029319</v>
@@ -5337,7 +5319,7 @@
       </c>
       <c r="S51" s="1"/>
       <c r="U51" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="V51">
         <v>25010105008</v>
@@ -5345,7 +5327,7 @@
     </row>
     <row r="52" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B52" s="10">
         <v>590029339</v>
@@ -5414,7 +5396,7 @@
       </c>
       <c r="S52" s="1"/>
       <c r="U52" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="V52">
         <v>25010105011</v>
@@ -5422,7 +5404,7 @@
     </row>
     <row r="53" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B53" s="10">
         <v>590029148</v>
@@ -5491,7 +5473,7 @@
       </c>
       <c r="S53" s="1"/>
       <c r="U53" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="V53">
         <v>25010104992</v>
@@ -5499,7 +5481,7 @@
     </row>
     <row r="54" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B54" s="10">
         <v>590029309</v>
@@ -5568,7 +5550,7 @@
       </c>
       <c r="S54" s="1"/>
       <c r="U54" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="V54">
         <v>25010104979</v>
@@ -5576,7 +5558,7 @@
     </row>
     <row r="55" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B55" s="10">
         <v>590028838</v>
@@ -5645,7 +5627,7 @@
       </c>
       <c r="S55" s="1"/>
       <c r="U55" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="V55">
         <v>25010104945</v>
@@ -5653,7 +5635,7 @@
     </row>
     <row r="56" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B56" s="10">
         <v>590029107</v>
@@ -5722,7 +5704,7 @@
       </c>
       <c r="S56" s="1"/>
       <c r="U56" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="V56">
         <v>25010104988</v>
@@ -5730,7 +5712,7 @@
     </row>
     <row r="57" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B57" s="10">
         <v>590029266</v>
@@ -5799,7 +5781,7 @@
       </c>
       <c r="S57" s="1"/>
       <c r="U57" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="V57">
         <v>25010104958</v>
@@ -5807,7 +5789,7 @@
     </row>
     <row r="58" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B58" s="10">
         <v>590029354</v>
@@ -5876,7 +5858,7 @@
       </c>
       <c r="S58" s="1"/>
       <c r="U58" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="V58">
         <v>25010105018</v>
@@ -5884,7 +5866,7 @@
     </row>
     <row r="59" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B59" s="10">
         <v>590029349</v>
@@ -5953,7 +5935,7 @@
       </c>
       <c r="S59" s="1"/>
       <c r="U59" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="V59">
         <v>25010105017</v>
@@ -5961,7 +5943,7 @@
     </row>
     <row r="60" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B60" s="10">
         <v>590029302</v>
@@ -6030,7 +6012,7 @@
       </c>
       <c r="S60" s="1"/>
       <c r="U60" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="V60">
         <v>25010104954</v>
@@ -6038,7 +6020,7 @@
     </row>
     <row r="61" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B61" s="10">
         <v>590029262</v>
@@ -6107,7 +6089,7 @@
       </c>
       <c r="S61" s="1"/>
       <c r="U61" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="V61">
         <v>25010104987</v>
@@ -6115,7 +6097,7 @@
     </row>
     <row r="62" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B62" s="10">
         <v>590029285</v>
@@ -6184,7 +6166,7 @@
       </c>
       <c r="S62" s="1"/>
       <c r="U62" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="V62">
         <v>25010104949</v>
@@ -6192,7 +6174,7 @@
     </row>
     <row r="63" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B63" s="10">
         <v>590029353</v>
@@ -6261,7 +6243,7 @@
       </c>
       <c r="S63" s="1"/>
       <c r="U63" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="V63">
         <v>122514758</v>
@@ -6269,7 +6251,7 @@
     </row>
     <row r="65" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C65" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="D65">
         <f>MAX(D5:D63)</f>
@@ -6338,7 +6320,7 @@
     </row>
     <row r="66" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C66" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="D66">
         <f>_xlfn.MINIFS(D5:D63, D5:D63, "&gt;0")</f>
@@ -6407,7 +6389,7 @@
     </row>
     <row r="67" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C67" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="D67">
         <f>MEDIAN(D5:D63)</f>
@@ -6476,7 +6458,7 @@
     </row>
     <row r="68" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C68" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="D68" cm="1">
         <f t="array" ref="D68">MEDIAN(_xlfn._xlws.FILTER(D5:D63, D5:D63&lt;&gt;0))</f>
@@ -6563,959 +6545,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C562E662-4892-4710-BFF6-3FF4023021A9}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:Q44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="26.7109375" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
-    <col min="6" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-    </row>
-    <row r="2" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="43"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B3" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="C3" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="44">
-        <v>46141</v>
-      </c>
-      <c r="G3" s="44">
-        <v>46142</v>
-      </c>
-      <c r="H3" s="44">
-        <v>46143</v>
-      </c>
-      <c r="I3" s="44">
-        <v>46147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="12">
-        <v>590029270</v>
-      </c>
-      <c r="D4" s="12">
-        <v>77</v>
-      </c>
-      <c r="E4" s="14">
-        <v>32</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="12">
-        <v>590029204</v>
-      </c>
-      <c r="D5" s="12">
-        <v>77</v>
-      </c>
-      <c r="E5" s="14">
-        <v>29</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>3</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="12">
-        <v>590029109</v>
-      </c>
-      <c r="D6" s="12">
-        <v>77</v>
-      </c>
-      <c r="E6" s="14">
-        <v>38</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>4</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="12">
-        <v>590029157</v>
-      </c>
-      <c r="D7" s="12">
-        <v>77</v>
-      </c>
-      <c r="E7" s="14">
-        <v>14</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>5</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="12">
-        <v>590029274</v>
-      </c>
-      <c r="D8" s="12">
-        <v>77</v>
-      </c>
-      <c r="E8" s="14">
-        <v>8</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>6</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="12">
-        <v>590029230</v>
-      </c>
-      <c r="D9" s="12">
-        <v>77</v>
-      </c>
-      <c r="E9" s="14">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>7</v>
-      </c>
-      <c r="B10" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="12">
-        <v>590029169</v>
-      </c>
-      <c r="D10" s="12">
-        <v>77</v>
-      </c>
-      <c r="E10" s="14">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>8</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="12">
-        <v>590029112</v>
-      </c>
-      <c r="D11" s="12">
-        <v>77</v>
-      </c>
-      <c r="E11" s="14">
-        <v>35</v>
-      </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>9</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="12">
-        <v>590029237</v>
-      </c>
-      <c r="D12" s="12">
-        <v>77</v>
-      </c>
-      <c r="E12" s="14">
-        <v>29</v>
-      </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>10</v>
-      </c>
-      <c r="B13" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="12">
-        <v>590029079</v>
-      </c>
-      <c r="D13" s="12">
-        <v>77</v>
-      </c>
-      <c r="E13" s="14">
-        <v>1</v>
-      </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>11</v>
-      </c>
-      <c r="B14" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="12">
-        <v>590029145</v>
-      </c>
-      <c r="D14" s="12">
-        <v>77</v>
-      </c>
-      <c r="E14" s="14">
-        <v>23</v>
-      </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>12</v>
-      </c>
-      <c r="B15" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="12">
-        <v>590029209</v>
-      </c>
-      <c r="D15" s="12">
-        <v>77</v>
-      </c>
-      <c r="E15" s="14">
-        <v>17</v>
-      </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>13</v>
-      </c>
-      <c r="B16" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="12">
-        <v>590027268</v>
-      </c>
-      <c r="D16" s="12">
-        <v>77</v>
-      </c>
-      <c r="E16" s="14">
-        <v>8</v>
-      </c>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>14</v>
-      </c>
-      <c r="B17" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="12">
-        <v>590023855</v>
-      </c>
-      <c r="D17" s="12">
-        <v>77</v>
-      </c>
-      <c r="E17" s="14">
-        <v>29</v>
-      </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>15</v>
-      </c>
-      <c r="B18" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="12">
-        <v>590029215</v>
-      </c>
-      <c r="D18" s="12">
-        <v>77</v>
-      </c>
-      <c r="E18" s="14">
-        <v>21</v>
-      </c>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>16</v>
-      </c>
-      <c r="B19" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="12">
-        <v>590029111</v>
-      </c>
-      <c r="D19" s="12">
-        <v>77</v>
-      </c>
-      <c r="E19" s="14">
-        <v>3</v>
-      </c>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>17</v>
-      </c>
-      <c r="B20" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" s="12">
-        <v>590028683</v>
-      </c>
-      <c r="D20" s="12">
-        <v>77</v>
-      </c>
-      <c r="E20" s="14">
-        <v>23</v>
-      </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>18</v>
-      </c>
-      <c r="B21" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21" s="12">
-        <v>590029048</v>
-      </c>
-      <c r="D21" s="12">
-        <v>77</v>
-      </c>
-      <c r="E21" s="14">
-        <v>26</v>
-      </c>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>19</v>
-      </c>
-      <c r="B22" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" s="12">
-        <v>590029330</v>
-      </c>
-      <c r="D22" s="12">
-        <v>78</v>
-      </c>
-      <c r="E22" s="14">
-        <v>38</v>
-      </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>20</v>
-      </c>
-      <c r="B23" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="12">
-        <v>590027630</v>
-      </c>
-      <c r="D23" s="12">
-        <v>78</v>
-      </c>
-      <c r="E23" s="14">
-        <v>0</v>
-      </c>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>21</v>
-      </c>
-      <c r="B24" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" s="12">
-        <v>590029219</v>
-      </c>
-      <c r="D24" s="12">
-        <v>78</v>
-      </c>
-      <c r="E24" s="14">
-        <v>31</v>
-      </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>22</v>
-      </c>
-      <c r="B25" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="C25" s="12">
-        <v>590027859</v>
-      </c>
-      <c r="D25" s="12">
-        <v>78</v>
-      </c>
-      <c r="E25" s="14">
-        <v>2</v>
-      </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>23</v>
-      </c>
-      <c r="B26" s="31" t="s">
-        <v>86</v>
-      </c>
-      <c r="C26" s="12">
-        <v>590023917</v>
-      </c>
-      <c r="D26" s="12">
-        <v>78</v>
-      </c>
-      <c r="E26" s="14">
-        <v>4</v>
-      </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>24</v>
-      </c>
-      <c r="B27" s="31" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" s="12">
-        <v>590023785</v>
-      </c>
-      <c r="D27" s="12">
-        <v>78</v>
-      </c>
-      <c r="E27" s="14">
-        <v>30</v>
-      </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>25</v>
-      </c>
-      <c r="B28" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" s="12">
-        <v>590029264</v>
-      </c>
-      <c r="D28" s="12">
-        <v>78</v>
-      </c>
-      <c r="E28" s="14">
-        <v>12</v>
-      </c>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>26</v>
-      </c>
-      <c r="B29" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="C29" s="12">
-        <v>590029042</v>
-      </c>
-      <c r="D29" s="12">
-        <v>78</v>
-      </c>
-      <c r="E29" s="14">
-        <v>0</v>
-      </c>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>27</v>
-      </c>
-      <c r="B30" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="C30" s="12">
-        <v>590029336</v>
-      </c>
-      <c r="D30" s="12">
-        <v>78</v>
-      </c>
-      <c r="E30" s="14">
-        <v>11</v>
-      </c>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>28</v>
-      </c>
-      <c r="B31" s="31" t="s">
-        <v>96</v>
-      </c>
-      <c r="C31" s="12">
-        <v>590029233</v>
-      </c>
-      <c r="D31" s="12">
-        <v>78</v>
-      </c>
-      <c r="E31" s="14">
-        <v>0</v>
-      </c>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>29</v>
-      </c>
-      <c r="B32" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="C32" s="12">
-        <v>590029328</v>
-      </c>
-      <c r="D32" s="12">
-        <v>78</v>
-      </c>
-      <c r="E32" s="14">
-        <v>10</v>
-      </c>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>30</v>
-      </c>
-      <c r="B33" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="C33" s="12">
-        <v>590028608</v>
-      </c>
-      <c r="D33" s="12">
-        <v>78</v>
-      </c>
-      <c r="E33" s="14">
-        <v>4</v>
-      </c>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>31</v>
-      </c>
-      <c r="B34" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="C34" s="12">
-        <v>590028605</v>
-      </c>
-      <c r="D34" s="12">
-        <v>78</v>
-      </c>
-      <c r="E34" s="14">
-        <v>0</v>
-      </c>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>32</v>
-      </c>
-      <c r="B35" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C35" s="12">
-        <v>590026626</v>
-      </c>
-      <c r="D35" s="12">
-        <v>78</v>
-      </c>
-      <c r="E35" s="14">
-        <v>0</v>
-      </c>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>33</v>
-      </c>
-      <c r="B36" s="31" t="s">
-        <v>108</v>
-      </c>
-      <c r="C36" s="12">
-        <v>590029319</v>
-      </c>
-      <c r="D36" s="12">
-        <v>78</v>
-      </c>
-      <c r="E36" s="14">
-        <v>1</v>
-      </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>34</v>
-      </c>
-      <c r="B37" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="C37" s="12">
-        <v>590029339</v>
-      </c>
-      <c r="D37" s="12">
-        <v>78</v>
-      </c>
-      <c r="E37" s="14">
-        <v>1</v>
-      </c>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>35</v>
-      </c>
-      <c r="B38" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="C38" s="12">
-        <v>590029148</v>
-      </c>
-      <c r="D38" s="12">
-        <v>78</v>
-      </c>
-      <c r="E38" s="14">
-        <v>17</v>
-      </c>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>36</v>
-      </c>
-      <c r="B39" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="C39" s="12">
-        <v>590029309</v>
-      </c>
-      <c r="D39" s="12">
-        <v>78</v>
-      </c>
-      <c r="E39" s="14">
-        <v>17</v>
-      </c>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>37</v>
-      </c>
-      <c r="B40" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="C40" s="12">
-        <v>590028838</v>
-      </c>
-      <c r="D40" s="12">
-        <v>78</v>
-      </c>
-      <c r="E40" s="14">
-        <v>0</v>
-      </c>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>38</v>
-      </c>
-      <c r="B41" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="C41" s="12">
-        <v>590029107</v>
-      </c>
-      <c r="D41" s="12">
-        <v>78</v>
-      </c>
-      <c r="E41" s="14">
-        <v>22</v>
-      </c>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>39</v>
-      </c>
-      <c r="B42" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="C42" s="12">
-        <v>590029266</v>
-      </c>
-      <c r="D42" s="12">
-        <v>78</v>
-      </c>
-      <c r="E42" s="14">
-        <v>9</v>
-      </c>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>40</v>
-      </c>
-      <c r="B43" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C43" s="12">
-        <v>590029349</v>
-      </c>
-      <c r="D43" s="12">
-        <v>78</v>
-      </c>
-      <c r="E43" s="14">
-        <v>31</v>
-      </c>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>41</v>
-      </c>
-      <c r="B44" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="C44" s="12">
-        <v>590029353</v>
-      </c>
-      <c r="D44" s="12">
-        <v>78</v>
-      </c>
-      <c r="E44" s="14">
-        <v>13</v>
-      </c>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="F2:I2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="84" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C77DC95-9EC1-40F8-9879-B4182E9CEA89}">
   <dimension ref="A1:F60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7530,22 +6559,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -7553,19 +6582,19 @@
         <v>590029330</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D2" s="22">
         <v>25010104997</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -7573,19 +6602,19 @@
         <v>590029213</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D3" s="22">
         <v>122507103</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -7593,19 +6622,19 @@
         <v>590027630</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D4" s="22">
         <v>25010105001</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -7613,19 +6642,19 @@
         <v>590029270</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D5" s="22">
         <v>25010104938</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -7633,19 +6662,19 @@
         <v>590029219</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D6" s="22">
         <v>25010104956</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -7653,19 +6682,19 @@
         <v>590029204</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D7" s="22">
         <v>25010104918</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -7673,19 +6702,19 @@
         <v>590029109</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D8" s="22">
         <v>25010104943</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -7693,19 +6722,19 @@
         <v>590028933</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D9" s="22">
         <v>25010104948</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -7713,19 +6742,19 @@
         <v>590029070</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D10" s="22">
         <v>25010104926</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -7733,19 +6762,19 @@
         <v>590027859</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D11" s="22">
         <v>25010104974</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -7753,19 +6782,19 @@
         <v>590029157</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D12" s="22">
         <v>25010104890</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -7773,19 +6802,19 @@
         <v>590027157</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D13" s="22">
         <v>25010104880</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -7793,19 +6822,19 @@
         <v>590028682</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D14" s="22">
         <v>25010104995</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -7813,19 +6842,19 @@
         <v>590023917</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D15" s="22">
         <v>25010105012</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -7833,19 +6862,19 @@
         <v>590023785</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D16" s="22">
         <v>25010104947</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -7853,19 +6882,19 @@
         <v>590029274</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D17" s="22">
         <v>25010104928</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -7873,19 +6902,19 @@
         <v>590029264</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D18" s="22">
         <v>25010104986</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -7893,19 +6922,19 @@
         <v>590029042</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D19" s="22">
         <v>25010104982</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -7913,19 +6942,19 @@
         <v>590029336</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D20" s="22">
         <v>25010104998</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -7933,19 +6962,19 @@
         <v>590028572</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D21" s="22">
         <v>25010104903</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -7953,19 +6982,19 @@
         <v>590029230</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D22" s="22">
         <v>25010104910</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -7973,19 +7002,19 @@
         <v>590029169</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D23" s="22">
         <v>25010104944</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -7993,19 +7022,19 @@
         <v>590029233</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D24" s="22">
         <v>25010104996</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -8013,19 +7042,19 @@
         <v>590029112</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D25" s="22">
         <v>25010104876</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -8033,19 +7062,19 @@
         <v>590025556</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D26" s="22">
         <v>122515743</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -8053,19 +7082,19 @@
         <v>590027830</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D27" s="22">
         <v>25010104886</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -8073,19 +7102,19 @@
         <v>590028360</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D28" s="22">
         <v>25010104881</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -8093,19 +7122,19 @@
         <v>590029237</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D29" s="22">
         <v>25010104909</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -8113,19 +7142,19 @@
         <v>590029328</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D30" s="22">
         <v>25010105010</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -8133,19 +7162,19 @@
         <v>590029079</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D31" s="22">
         <v>25010104906</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -8153,19 +7182,19 @@
         <v>590029145</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D32" s="22">
         <v>25010104892</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -8173,19 +7202,19 @@
         <v>590029209</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D33" s="22">
         <v>25010104887</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -8193,19 +7222,19 @@
         <v>590027268</v>
       </c>
       <c r="B34" s="22" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D34" s="22">
         <v>25010104933</v>
       </c>
       <c r="E34" s="22" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="F34" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -8213,19 +7242,19 @@
         <v>590029227</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D35" s="22">
         <v>25010104900</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F35" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -8233,19 +7262,19 @@
         <v>590029241</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D36" s="22">
         <v>25010104915</v>
       </c>
       <c r="E36" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F36" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -8253,19 +7282,19 @@
         <v>590023855</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D37" s="22">
         <v>25010104868</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F37" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -8273,19 +7302,19 @@
         <v>590028608</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D38" s="22">
         <v>25010104999</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F38" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -8293,19 +7322,19 @@
         <v>590029215</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D39" s="22">
         <v>25010104884</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F39" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -8313,19 +7342,19 @@
         <v>590029111</v>
       </c>
       <c r="B40" s="22" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D40" s="22">
         <v>25010104888</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F40" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -8333,19 +7362,19 @@
         <v>590028605</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D41" s="22">
         <v>25010104326</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F41" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -8353,19 +7382,19 @@
         <v>590028683</v>
       </c>
       <c r="B42" s="22" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D42" s="22">
         <v>25010104936</v>
       </c>
       <c r="E42" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F42" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -8373,19 +7402,19 @@
         <v>590029121</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D43" s="22">
         <v>25010104875</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F43" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -8393,19 +7422,19 @@
         <v>590026626</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D44" s="22">
         <v>25010104601</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F44" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -8413,19 +7442,19 @@
         <v>590029310</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D45" s="22">
         <v>25010104970</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F45" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -8433,19 +7462,19 @@
         <v>590029319</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D46" s="22">
         <v>25010105008</v>
       </c>
       <c r="E46" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F46" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -8453,19 +7482,19 @@
         <v>590029048</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D47" s="22">
         <v>25010104925</v>
       </c>
       <c r="E47" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F47" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -8473,19 +7502,19 @@
         <v>590029184</v>
       </c>
       <c r="B48" s="22" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D48" s="22">
         <v>25010104879</v>
       </c>
       <c r="E48" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F48" s="22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -8493,19 +7522,19 @@
         <v>590029339</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D49" s="22">
         <v>25010105011</v>
       </c>
       <c r="E49" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F49" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -8513,19 +7542,19 @@
         <v>590029148</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D50" s="22">
         <v>25010104992</v>
       </c>
       <c r="E50" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F50" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -8533,19 +7562,19 @@
         <v>590029309</v>
       </c>
       <c r="B51" s="22" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D51" s="22">
         <v>25010104979</v>
       </c>
       <c r="E51" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F51" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -8553,19 +7582,19 @@
         <v>590028838</v>
       </c>
       <c r="B52" s="22" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D52" s="22">
         <v>25010104945</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F52" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -8573,19 +7602,19 @@
         <v>590029107</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D53" s="22">
         <v>25010104988</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F53" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -8593,19 +7622,19 @@
         <v>590029266</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D54" s="22">
         <v>25010104958</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F54" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -8613,19 +7642,19 @@
         <v>590029354</v>
       </c>
       <c r="B55" s="22" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C55" s="22" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D55" s="22">
         <v>25010105018</v>
       </c>
       <c r="E55" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F55" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -8633,19 +7662,19 @@
         <v>590029349</v>
       </c>
       <c r="B56" s="22" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D56" s="22">
         <v>25010105017</v>
       </c>
       <c r="E56" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F56" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -8653,19 +7682,19 @@
         <v>590029302</v>
       </c>
       <c r="B57" s="22" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D57" s="22">
         <v>25010104954</v>
       </c>
       <c r="E57" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F57" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -8673,19 +7702,19 @@
         <v>590029262</v>
       </c>
       <c r="B58" s="22" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D58" s="22">
         <v>25010104987</v>
       </c>
       <c r="E58" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F58" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -8693,19 +7722,19 @@
         <v>590029285</v>
       </c>
       <c r="B59" s="22" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D59" s="22">
         <v>25010104949</v>
       </c>
       <c r="E59" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F59" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -8713,19 +7742,19 @@
         <v>590029353</v>
       </c>
       <c r="B60" s="22" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D60" s="22">
         <v>122514758</v>
       </c>
       <c r="E60" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F60" s="22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -8736,7 +7765,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F2A4200-FA0B-463F-B62D-57714FA2A6D5}">
   <dimension ref="A1:G60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8751,25 +7780,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="C1" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="D1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="E1" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="F1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -8777,19 +7806,19 @@
         <v>590029213</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D2">
         <v>122507103</v>
       </c>
       <c r="E2" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F2" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -8797,19 +7826,19 @@
         <v>590029270</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D3">
         <v>25010104938</v>
       </c>
       <c r="E3" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F3" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -8817,19 +7846,19 @@
         <v>590029204</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D4">
         <v>25010104918</v>
       </c>
       <c r="E4" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F4" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -8837,19 +7866,19 @@
         <v>590029109</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D5">
         <v>25010104943</v>
       </c>
       <c r="E5" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F5" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -8857,19 +7886,19 @@
         <v>590029070</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D6">
         <v>25010104926</v>
       </c>
       <c r="E6" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F6" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -8877,19 +7906,19 @@
         <v>590029157</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D7">
         <v>25010104890</v>
       </c>
       <c r="E7" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F7" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -8897,19 +7926,19 @@
         <v>590027157</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D8">
         <v>25010104880</v>
       </c>
       <c r="E8" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F8" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -8917,19 +7946,19 @@
         <v>590029274</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D9">
         <v>25010104928</v>
       </c>
       <c r="E9" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F9" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -8937,19 +7966,19 @@
         <v>590028572</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D10">
         <v>25010104903</v>
       </c>
       <c r="E10" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F10" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -8957,19 +7986,19 @@
         <v>590029230</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D11">
         <v>25010104910</v>
       </c>
       <c r="E11" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F11" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -8977,19 +8006,19 @@
         <v>590029169</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D12">
         <v>25010104944</v>
       </c>
       <c r="E12" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F12" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -8997,19 +8026,19 @@
         <v>590029112</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D13">
         <v>25010104876</v>
       </c>
       <c r="E13" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F13" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -9017,19 +8046,19 @@
         <v>590025556</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D14">
         <v>122515743</v>
       </c>
       <c r="E14" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F14" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -9037,19 +8066,19 @@
         <v>590027830</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D15">
         <v>25010104886</v>
       </c>
       <c r="E15" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F15" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -9057,19 +8086,19 @@
         <v>590028360</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D16">
         <v>25010104881</v>
       </c>
       <c r="E16" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F16" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -9077,19 +8106,19 @@
         <v>590029237</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D17">
         <v>25010104909</v>
       </c>
       <c r="E17" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F17" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -9097,19 +8126,19 @@
         <v>590029079</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D18">
         <v>25010104906</v>
       </c>
       <c r="E18" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F18" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -9117,19 +8146,19 @@
         <v>590029145</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D19">
         <v>25010104892</v>
       </c>
       <c r="E19" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F19" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -9137,19 +8166,19 @@
         <v>590029209</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D20">
         <v>25010104887</v>
       </c>
       <c r="E20" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F20" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -9157,19 +8186,19 @@
         <v>590027268</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D21">
         <v>25010104933</v>
       </c>
       <c r="E21" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="F21" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -9177,19 +8206,19 @@
         <v>590029227</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D22">
         <v>25010104900</v>
       </c>
       <c r="E22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -9197,19 +8226,19 @@
         <v>590029241</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D23">
         <v>25010104915</v>
       </c>
       <c r="E23" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F23" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -9217,19 +8246,19 @@
         <v>590023855</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C24" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D24">
         <v>25010104868</v>
       </c>
       <c r="E24" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F24" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -9237,19 +8266,19 @@
         <v>590029215</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D25">
         <v>25010104884</v>
       </c>
       <c r="E25" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -9257,19 +8286,19 @@
         <v>590029111</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D26">
         <v>25010104888</v>
       </c>
       <c r="E26" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F26" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -9277,19 +8306,19 @@
         <v>590028683</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D27">
         <v>25010104936</v>
       </c>
       <c r="E27" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F27" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -9297,19 +8326,19 @@
         <v>590029121</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D28">
         <v>25010104875</v>
       </c>
       <c r="E28" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F28" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -9317,19 +8346,19 @@
         <v>590029048</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C29" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D29">
         <v>25010104925</v>
       </c>
       <c r="E29" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F29" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -9337,19 +8366,19 @@
         <v>590029184</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C30" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D30">
         <v>25010104879</v>
       </c>
       <c r="E30" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F30" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -9357,19 +8386,19 @@
         <v>590029330</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D31">
         <v>25010104997</v>
       </c>
       <c r="E31" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F31" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -9380,19 +8409,19 @@
         <v>590027630</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C32" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D32">
         <v>25010105001</v>
       </c>
       <c r="E32" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F32" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -9403,19 +8432,19 @@
         <v>590029219</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C33" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D33">
         <v>25010104956</v>
       </c>
       <c r="E33" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F33" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -9426,19 +8455,19 @@
         <v>590028933</v>
       </c>
       <c r="B34" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C34" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D34">
         <v>25010104948</v>
       </c>
       <c r="E34" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F34" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -9449,19 +8478,19 @@
         <v>590027859</v>
       </c>
       <c r="B35" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C35" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D35">
         <v>25010104974</v>
       </c>
       <c r="E35" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F35" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -9472,19 +8501,19 @@
         <v>590028682</v>
       </c>
       <c r="B36" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C36" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D36">
         <v>25010104995</v>
       </c>
       <c r="E36" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F36" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -9495,19 +8524,19 @@
         <v>590023917</v>
       </c>
       <c r="B37" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C37" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D37">
         <v>25010105012</v>
       </c>
       <c r="E37" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F37" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -9518,19 +8547,19 @@
         <v>590023785</v>
       </c>
       <c r="B38" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C38" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D38">
         <v>25010104947</v>
       </c>
       <c r="E38" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F38" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G38">
         <v>2</v>
@@ -9541,19 +8570,19 @@
         <v>590029264</v>
       </c>
       <c r="B39" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C39" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D39">
         <v>25010104986</v>
       </c>
       <c r="E39" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F39" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G39">
         <v>2</v>
@@ -9564,19 +8593,19 @@
         <v>590029042</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C40" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D40">
         <v>25010104982</v>
       </c>
       <c r="E40" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F40" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G40">
         <v>2</v>
@@ -9587,19 +8616,19 @@
         <v>590029336</v>
       </c>
       <c r="B41" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C41" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D41">
         <v>25010104998</v>
       </c>
       <c r="E41" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F41" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G41">
         <v>3</v>
@@ -9610,19 +8639,19 @@
         <v>590029233</v>
       </c>
       <c r="B42" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C42" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D42">
         <v>25010104996</v>
       </c>
       <c r="E42" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F42" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G42">
         <v>3</v>
@@ -9633,19 +8662,19 @@
         <v>590029328</v>
       </c>
       <c r="B43" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C43" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D43">
         <v>25010105010</v>
       </c>
       <c r="E43" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F43" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G43">
         <v>3</v>
@@ -9656,19 +8685,19 @@
         <v>590028608</v>
       </c>
       <c r="B44" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C44" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D44">
         <v>25010104999</v>
       </c>
       <c r="E44" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F44" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G44">
         <v>3</v>
@@ -9679,19 +8708,19 @@
         <v>590028605</v>
       </c>
       <c r="B45" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C45" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D45">
         <v>25010104326</v>
       </c>
       <c r="E45" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F45" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G45">
         <v>3</v>
@@ -9702,19 +8731,19 @@
         <v>590026626</v>
       </c>
       <c r="B46" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C46" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D46">
         <v>25010104601</v>
       </c>
       <c r="E46" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F46" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G46">
         <v>4</v>
@@ -9725,19 +8754,19 @@
         <v>590029310</v>
       </c>
       <c r="B47" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C47" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D47">
         <v>25010104970</v>
       </c>
       <c r="E47" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F47" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G47">
         <v>4</v>
@@ -9748,19 +8777,19 @@
         <v>590029319</v>
       </c>
       <c r="B48" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C48" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D48">
         <v>25010105008</v>
       </c>
       <c r="E48" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F48" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G48">
         <v>4</v>
@@ -9771,19 +8800,19 @@
         <v>590029339</v>
       </c>
       <c r="B49" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C49" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D49">
         <v>25010105011</v>
       </c>
       <c r="E49" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F49" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G49">
         <v>4</v>
@@ -9794,19 +8823,19 @@
         <v>590029148</v>
       </c>
       <c r="B50" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C50" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D50">
         <v>25010104992</v>
       </c>
       <c r="E50" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F50" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G50">
         <v>4</v>
@@ -9817,19 +8846,19 @@
         <v>590029309</v>
       </c>
       <c r="B51" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C51" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D51">
         <v>25010104979</v>
       </c>
       <c r="E51" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F51" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G51">
         <v>5</v>
@@ -9840,19 +8869,19 @@
         <v>590028838</v>
       </c>
       <c r="B52" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C52" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D52">
         <v>25010104945</v>
       </c>
       <c r="E52" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F52" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G52">
         <v>5</v>
@@ -9863,19 +8892,19 @@
         <v>590029107</v>
       </c>
       <c r="B53" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C53" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D53">
         <v>25010104988</v>
       </c>
       <c r="E53" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F53" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G53">
         <v>5</v>
@@ -9886,19 +8915,19 @@
         <v>590029266</v>
       </c>
       <c r="B54" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C54" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D54">
         <v>25010104958</v>
       </c>
       <c r="E54" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F54" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G54">
         <v>5</v>
@@ -9909,19 +8938,19 @@
         <v>590029354</v>
       </c>
       <c r="B55" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C55" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D55">
         <v>25010105018</v>
       </c>
       <c r="E55" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F55" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G55">
         <v>5</v>
@@ -9932,19 +8961,19 @@
         <v>590029349</v>
       </c>
       <c r="B56" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C56" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D56">
         <v>25010105017</v>
       </c>
       <c r="E56" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F56" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G56">
         <v>6</v>
@@ -9955,19 +8984,19 @@
         <v>590029302</v>
       </c>
       <c r="B57" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C57" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D57">
         <v>25010104954</v>
       </c>
       <c r="E57" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F57" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G57">
         <v>6</v>
@@ -9978,19 +9007,19 @@
         <v>590029262</v>
       </c>
       <c r="B58" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C58" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D58">
         <v>25010104987</v>
       </c>
       <c r="E58" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F58" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G58">
         <v>6</v>
@@ -10001,19 +9030,19 @@
         <v>590029285</v>
       </c>
       <c r="B59" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C59" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D59">
         <v>25010104949</v>
       </c>
       <c r="E59" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F59" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G59">
         <v>6</v>
@@ -10024,25 +9053,1181 @@
         <v>590029353</v>
       </c>
       <c r="B60" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C60" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D60">
         <v>122514758</v>
       </c>
       <c r="E60" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F60" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="G60">
         <v>6</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2A64475-D0FD-4D20-815F-B70A60B2F951}">
+  <dimension ref="A1:F64"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.42578125" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="24.75" x14ac:dyDescent="0.4">
+      <c r="A1" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+    </row>
+    <row r="2" spans="1:6" ht="24.75" x14ac:dyDescent="0.4">
+      <c r="A2" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="37" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="B4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="14">
+        <v>100</v>
+      </c>
+      <c r="E4" s="5">
+        <f>SUM(D4)</f>
+        <v>100</v>
+      </c>
+      <c r="F4" s="5"/>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="1">
+        <v>590029213</v>
+      </c>
+      <c r="C5" s="12">
+        <v>77</v>
+      </c>
+      <c r="D5" s="29">
+        <v>95.5</v>
+      </c>
+      <c r="E5" s="26">
+        <f>SUM(D5)</f>
+        <v>95.5</v>
+      </c>
+      <c r="F5" s="39"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="1">
+        <v>590029270</v>
+      </c>
+      <c r="C6" s="12">
+        <v>77</v>
+      </c>
+      <c r="D6" s="29">
+        <v>39</v>
+      </c>
+      <c r="E6" s="26">
+        <f t="shared" ref="E6:E63" si="0">SUM(D6)</f>
+        <v>39</v>
+      </c>
+      <c r="F6" s="39"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="1">
+        <v>590029204</v>
+      </c>
+      <c r="C7" s="12">
+        <v>77</v>
+      </c>
+      <c r="D7" s="29">
+        <v>73.5</v>
+      </c>
+      <c r="E7" s="26">
+        <f t="shared" si="0"/>
+        <v>73.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="1">
+        <v>590029109</v>
+      </c>
+      <c r="C8" s="12">
+        <v>77</v>
+      </c>
+      <c r="D8" s="29">
+        <v>54.5</v>
+      </c>
+      <c r="E8" s="26">
+        <f t="shared" si="0"/>
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="1">
+        <v>590029070</v>
+      </c>
+      <c r="C9" s="12">
+        <v>77</v>
+      </c>
+      <c r="D9" s="29">
+        <v>97.5</v>
+      </c>
+      <c r="E9" s="26">
+        <f t="shared" si="0"/>
+        <v>97.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="1">
+        <v>590029157</v>
+      </c>
+      <c r="C10" s="12">
+        <v>77</v>
+      </c>
+      <c r="D10" s="29">
+        <v>40</v>
+      </c>
+      <c r="E10" s="26">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="1">
+        <v>590027157</v>
+      </c>
+      <c r="C11" s="12">
+        <v>77</v>
+      </c>
+      <c r="D11" s="29">
+        <v>54</v>
+      </c>
+      <c r="E11" s="26">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="1">
+        <v>590029274</v>
+      </c>
+      <c r="C12" s="12">
+        <v>77</v>
+      </c>
+      <c r="D12" s="29">
+        <v>44.5</v>
+      </c>
+      <c r="E12" s="26">
+        <f t="shared" si="0"/>
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="1">
+        <v>590028572</v>
+      </c>
+      <c r="C13" s="12">
+        <v>77</v>
+      </c>
+      <c r="D13" s="29">
+        <v>98</v>
+      </c>
+      <c r="E13" s="26">
+        <f t="shared" si="0"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="1">
+        <v>590029230</v>
+      </c>
+      <c r="C14" s="12">
+        <v>77</v>
+      </c>
+      <c r="D14" s="29">
+        <v>0</v>
+      </c>
+      <c r="E14" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="1">
+        <v>590029169</v>
+      </c>
+      <c r="C15" s="12">
+        <v>77</v>
+      </c>
+      <c r="D15" s="29">
+        <v>39</v>
+      </c>
+      <c r="E15" s="26">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="1">
+        <v>590029112</v>
+      </c>
+      <c r="C16" s="12">
+        <v>77</v>
+      </c>
+      <c r="D16" s="29">
+        <v>65</v>
+      </c>
+      <c r="E16" s="26">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="1">
+        <v>590025556</v>
+      </c>
+      <c r="C17" s="12">
+        <v>77</v>
+      </c>
+      <c r="D17" s="29">
+        <v>68.5</v>
+      </c>
+      <c r="E17" s="26">
+        <f t="shared" si="0"/>
+        <v>68.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="1">
+        <v>590027830</v>
+      </c>
+      <c r="C18" s="12">
+        <v>77</v>
+      </c>
+      <c r="D18" s="29">
+        <v>85.5</v>
+      </c>
+      <c r="E18" s="26">
+        <f t="shared" si="0"/>
+        <v>85.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="1">
+        <v>590028360</v>
+      </c>
+      <c r="C19" s="12">
+        <v>77</v>
+      </c>
+      <c r="D19" s="29">
+        <v>84.5</v>
+      </c>
+      <c r="E19" s="26">
+        <f t="shared" si="0"/>
+        <v>84.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="1">
+        <v>590029237</v>
+      </c>
+      <c r="C20" s="12">
+        <v>77</v>
+      </c>
+      <c r="D20" s="29">
+        <v>51</v>
+      </c>
+      <c r="E20" s="26">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="1">
+        <v>590029079</v>
+      </c>
+      <c r="C21" s="12">
+        <v>77</v>
+      </c>
+      <c r="D21" s="29">
+        <v>0</v>
+      </c>
+      <c r="E21" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="1">
+        <v>590029145</v>
+      </c>
+      <c r="C22" s="12">
+        <v>77</v>
+      </c>
+      <c r="D22" s="29">
+        <v>67</v>
+      </c>
+      <c r="E22" s="26">
+        <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="1">
+        <v>590029209</v>
+      </c>
+      <c r="C23" s="12">
+        <v>77</v>
+      </c>
+      <c r="D23" s="29">
+        <v>28</v>
+      </c>
+      <c r="E23" s="26">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" s="1">
+        <v>590027268</v>
+      </c>
+      <c r="C24" s="12">
+        <v>77</v>
+      </c>
+      <c r="D24" s="29">
+        <v>46.5</v>
+      </c>
+      <c r="E24" s="26">
+        <f t="shared" si="0"/>
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" s="1">
+        <v>590029227</v>
+      </c>
+      <c r="C25" s="12">
+        <v>77</v>
+      </c>
+      <c r="D25" s="29">
+        <v>93.5</v>
+      </c>
+      <c r="E25" s="26">
+        <f t="shared" si="0"/>
+        <v>93.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" s="1">
+        <v>590029241</v>
+      </c>
+      <c r="C26" s="12">
+        <v>77</v>
+      </c>
+      <c r="D26" s="29">
+        <v>76</v>
+      </c>
+      <c r="E26" s="26">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="1">
+        <v>590023855</v>
+      </c>
+      <c r="C27" s="12">
+        <v>77</v>
+      </c>
+      <c r="D27" s="29">
+        <v>29</v>
+      </c>
+      <c r="E27" s="26">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="1">
+        <v>590029215</v>
+      </c>
+      <c r="C28" s="12">
+        <v>77</v>
+      </c>
+      <c r="D28" s="29">
+        <v>52.5</v>
+      </c>
+      <c r="E28" s="26">
+        <f t="shared" si="0"/>
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" s="1">
+        <v>590029111</v>
+      </c>
+      <c r="C29" s="12">
+        <v>77</v>
+      </c>
+      <c r="D29" s="29">
+        <v>45</v>
+      </c>
+      <c r="E29" s="26">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" s="1">
+        <v>590028683</v>
+      </c>
+      <c r="C30" s="12">
+        <v>77</v>
+      </c>
+      <c r="D30" s="29">
+        <v>78.5</v>
+      </c>
+      <c r="E30" s="26">
+        <f t="shared" si="0"/>
+        <v>78.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="1">
+        <v>590029121</v>
+      </c>
+      <c r="C31" s="12">
+        <v>77</v>
+      </c>
+      <c r="D31" s="29">
+        <v>90.5</v>
+      </c>
+      <c r="E31" s="26">
+        <f t="shared" si="0"/>
+        <v>90.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" s="1">
+        <v>590029048</v>
+      </c>
+      <c r="C32" s="12">
+        <v>77</v>
+      </c>
+      <c r="D32" s="29">
+        <v>83</v>
+      </c>
+      <c r="E32" s="26">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" s="1">
+        <v>590029184</v>
+      </c>
+      <c r="C33" s="12">
+        <v>77</v>
+      </c>
+      <c r="D33" s="29">
+        <v>75.5</v>
+      </c>
+      <c r="E33" s="26">
+        <f t="shared" si="0"/>
+        <v>75.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" s="1">
+        <v>590029330</v>
+      </c>
+      <c r="C34" s="12">
+        <v>78</v>
+      </c>
+      <c r="D34" s="29">
+        <v>62.5</v>
+      </c>
+      <c r="E34" s="26">
+        <f t="shared" si="0"/>
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" s="1">
+        <v>590027630</v>
+      </c>
+      <c r="C35" s="12">
+        <v>78</v>
+      </c>
+      <c r="D35" s="29">
+        <v>43.5</v>
+      </c>
+      <c r="E35" s="26">
+        <f t="shared" si="0"/>
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B36" s="1">
+        <v>590029219</v>
+      </c>
+      <c r="C36" s="12">
+        <v>78</v>
+      </c>
+      <c r="D36" s="29">
+        <v>68</v>
+      </c>
+      <c r="E36" s="26">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" s="1">
+        <v>590028933</v>
+      </c>
+      <c r="C37" s="12">
+        <v>78</v>
+      </c>
+      <c r="D37" s="29">
+        <v>66.5</v>
+      </c>
+      <c r="E37" s="26">
+        <f t="shared" si="0"/>
+        <v>66.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B38" s="1">
+        <v>590027859</v>
+      </c>
+      <c r="C38" s="12">
+        <v>78</v>
+      </c>
+      <c r="D38" s="29">
+        <v>40</v>
+      </c>
+      <c r="E38" s="26">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B39" s="1">
+        <v>590028682</v>
+      </c>
+      <c r="C39" s="12">
+        <v>78</v>
+      </c>
+      <c r="D39" s="29">
+        <v>39</v>
+      </c>
+      <c r="E39" s="26">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" s="1">
+        <v>590023917</v>
+      </c>
+      <c r="C40" s="12">
+        <v>78</v>
+      </c>
+      <c r="D40" s="29">
+        <v>39</v>
+      </c>
+      <c r="E40" s="26">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="1">
+        <v>590023785</v>
+      </c>
+      <c r="C41" s="12">
+        <v>78</v>
+      </c>
+      <c r="D41" s="29">
+        <v>68.5</v>
+      </c>
+      <c r="E41" s="26">
+        <f t="shared" si="0"/>
+        <v>68.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" s="1">
+        <v>590029264</v>
+      </c>
+      <c r="C42" s="12">
+        <v>78</v>
+      </c>
+      <c r="D42" s="29">
+        <v>16</v>
+      </c>
+      <c r="E42" s="26">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B43" s="1">
+        <v>590029042</v>
+      </c>
+      <c r="C43" s="12">
+        <v>78</v>
+      </c>
+      <c r="D43" s="29">
+        <v>0</v>
+      </c>
+      <c r="E43" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B44" s="1">
+        <v>590029336</v>
+      </c>
+      <c r="C44" s="12">
+        <v>78</v>
+      </c>
+      <c r="D44" s="29">
+        <v>70</v>
+      </c>
+      <c r="E44" s="26">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B45" s="1">
+        <v>590029233</v>
+      </c>
+      <c r="C45" s="12">
+        <v>78</v>
+      </c>
+      <c r="D45" s="29">
+        <v>5</v>
+      </c>
+      <c r="E45" s="26">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B46" s="1">
+        <v>590029328</v>
+      </c>
+      <c r="C46" s="12">
+        <v>78</v>
+      </c>
+      <c r="D46" s="29">
+        <v>48</v>
+      </c>
+      <c r="E46" s="26">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B47" s="1">
+        <v>590028608</v>
+      </c>
+      <c r="C47" s="12">
+        <v>78</v>
+      </c>
+      <c r="D47" s="29">
+        <v>27</v>
+      </c>
+      <c r="E47" s="26">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B48" s="1">
+        <v>590028605</v>
+      </c>
+      <c r="C48" s="12">
+        <v>78</v>
+      </c>
+      <c r="D48" s="29">
+        <v>53</v>
+      </c>
+      <c r="E48" s="26">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" s="1">
+        <v>590026626</v>
+      </c>
+      <c r="C49" s="12">
+        <v>78</v>
+      </c>
+      <c r="D49" s="29">
+        <v>0</v>
+      </c>
+      <c r="E49" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B50" s="1">
+        <v>590029310</v>
+      </c>
+      <c r="C50" s="12">
+        <v>78</v>
+      </c>
+      <c r="D50" s="29">
+        <v>70.5</v>
+      </c>
+      <c r="E50" s="26">
+        <f t="shared" si="0"/>
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B51" s="1">
+        <v>590029319</v>
+      </c>
+      <c r="C51" s="12">
+        <v>78</v>
+      </c>
+      <c r="D51" s="29">
+        <v>40</v>
+      </c>
+      <c r="E51" s="26">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B52" s="1">
+        <v>590029339</v>
+      </c>
+      <c r="C52" s="12">
+        <v>78</v>
+      </c>
+      <c r="D52" s="29">
+        <v>0</v>
+      </c>
+      <c r="E52" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B53" s="1">
+        <v>590029148</v>
+      </c>
+      <c r="C53" s="12">
+        <v>78</v>
+      </c>
+      <c r="D53" s="29">
+        <v>46</v>
+      </c>
+      <c r="E53" s="26">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B54" s="1">
+        <v>590029309</v>
+      </c>
+      <c r="C54" s="12">
+        <v>78</v>
+      </c>
+      <c r="D54" s="29">
+        <v>52.5</v>
+      </c>
+      <c r="E54" s="26">
+        <f t="shared" si="0"/>
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B55" s="1">
+        <v>590028838</v>
+      </c>
+      <c r="C55" s="12">
+        <v>78</v>
+      </c>
+      <c r="D55" s="29">
+        <v>37</v>
+      </c>
+      <c r="E55" s="26">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B56" s="1">
+        <v>590029107</v>
+      </c>
+      <c r="C56" s="12">
+        <v>78</v>
+      </c>
+      <c r="D56" s="29">
+        <v>23</v>
+      </c>
+      <c r="E56" s="26">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B57" s="1">
+        <v>590029266</v>
+      </c>
+      <c r="C57" s="12">
+        <v>78</v>
+      </c>
+      <c r="D57" s="29">
+        <v>8.5</v>
+      </c>
+      <c r="E57" s="26">
+        <f t="shared" si="0"/>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B58" s="1">
+        <v>590029354</v>
+      </c>
+      <c r="C58" s="12">
+        <v>78</v>
+      </c>
+      <c r="D58" s="29">
+        <v>80</v>
+      </c>
+      <c r="E58" s="26">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B59" s="1">
+        <v>590029349</v>
+      </c>
+      <c r="C59" s="12">
+        <v>78</v>
+      </c>
+      <c r="D59" s="29">
+        <v>67</v>
+      </c>
+      <c r="E59" s="26">
+        <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B60" s="1">
+        <v>590029302</v>
+      </c>
+      <c r="C60" s="12">
+        <v>78</v>
+      </c>
+      <c r="D60" s="29">
+        <v>80</v>
+      </c>
+      <c r="E60" s="26">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B61" s="1">
+        <v>590029262</v>
+      </c>
+      <c r="C61" s="12">
+        <v>78</v>
+      </c>
+      <c r="D61" s="29">
+        <v>51.5</v>
+      </c>
+      <c r="E61" s="26">
+        <f t="shared" si="0"/>
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B62" s="1">
+        <v>590029285</v>
+      </c>
+      <c r="C62" s="12">
+        <v>78</v>
+      </c>
+      <c r="D62" s="29">
+        <v>51</v>
+      </c>
+      <c r="E62" s="26">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B63" s="1">
+        <v>590029353</v>
+      </c>
+      <c r="C63" s="12">
+        <v>78</v>
+      </c>
+      <c r="D63" s="29">
+        <v>70</v>
+      </c>
+      <c r="E63" s="26">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="29"/>
+      <c r="E64" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E5:E64">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -10061,150 +10246,150 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="47" t="s">
-        <v>162</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
+      <c r="A1" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
     </row>
     <row r="2" spans="1:21" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="47" t="str">
+      <c r="A2" s="44" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Physics for Computer Engineers (PHYS 1036) </v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="S3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
@@ -13692,69 +13877,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="47" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
+      <c r="A1" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
     </row>
     <row r="2" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="47" t="str">
+      <c r="A2" s="44" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Physics for Computer Engineers (PHYS 1036) </v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -13765,37 +13950,37 @@
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
       <c r="T3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -13804,21 +13989,21 @@
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5">
@@ -17012,147 +17197,147 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="47" t="s">
-        <v>134</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
+      <c r="A1" s="44" t="s">
+        <v>159</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
     </row>
     <row r="2" spans="1:21" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="47" t="str">
+      <c r="A2" s="44" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Physics for Computer Engineers (PHYS 1036) </v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
       <c r="D3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="S3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="G4" s="34" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="H4" s="34" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="I4" s="34" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="J4" s="34" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="K4" s="34" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="L4" s="34" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="M4" s="34" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="N4" s="34" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="O4" s="34" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="30"/>
       <c r="B5" s="8" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8">
@@ -20581,134 +20766,134 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="47" t="s">
-        <v>151</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
+      <c r="A1" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
     </row>
     <row r="2" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="47" t="str">
+      <c r="A2" s="44" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Physics for Computer Engineers (PHYS 1036) </v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="16"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="J4" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="18"/>
       <c r="B5" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C5" s="5">
         <v>4</v>
@@ -21604,152 +21789,152 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="47" t="s">
-        <v>163</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
+      <c r="A1" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
     </row>
     <row r="2" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="47" t="str">
+      <c r="A2" s="44" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Physics for Computer Engineers (PHYS 1036) </v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="2" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="S3" s="2" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
@@ -25286,141 +25471,141 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="47" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
+      <c r="A1" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
     </row>
     <row r="2" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="47" t="str">
+      <c r="A2" s="44" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Physics for Computer Engineers (PHYS 1036) </v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
       <c r="R3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="J4" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C5" s="5">
         <v>20</v>
@@ -29128,61 +29313,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="47" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
+      <c r="A1" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
     </row>
     <row r="2" spans="1:21" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="47" t="str">
+      <c r="A2" s="44" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Physics for Computer Engineers (PHYS 1036) </v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -29193,36 +29378,36 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
       <c r="R3" s="2" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -29231,22 +29416,22 @@
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="7" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C5" s="5">
         <v>3</v>
@@ -31891,67 +32076,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
+      <c r="A1" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
     </row>
     <row r="2" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="47" t="str">
+      <c r="A2" s="44" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Physics for Computer Engineers (PHYS 1036) </v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="2" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -31961,76 +32146,76 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="S3" s="2" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="D5" s="5">
         <v>2</v>
@@ -32117,19 +32302,19 @@
         <v>15</v>
       </c>
       <c r="P6" s="1"/>
-      <c r="S6" s="46">
+      <c r="S6" s="43">
         <f t="shared" ref="S6:S65" si="0">SUM(D6:E6)</f>
         <v>3.5</v>
       </c>
-      <c r="T6" s="46">
+      <c r="T6" s="43">
         <f t="shared" ref="T6:T65" si="1">SUM(G6,I6)</f>
         <v>4</v>
       </c>
-      <c r="U6" s="46">
+      <c r="U6" s="43">
         <f t="shared" ref="U6:U65" si="2">SUM(F6,H6)</f>
         <v>7.5</v>
       </c>
-      <c r="V6" s="46">
+      <c r="V6" s="43">
         <f t="shared" ref="V6:V65" si="3">SUM(S6:U6)</f>
         <v>15</v>
       </c>
@@ -32174,19 +32359,19 @@
         <v>11.5</v>
       </c>
       <c r="P7" s="1"/>
-      <c r="S7" s="46">
+      <c r="S7" s="43">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="T7" s="46">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="U7" s="46">
+      <c r="T7" s="43">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="U7" s="43">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="V7" s="46">
+      <c r="V7" s="43">
         <f t="shared" si="3"/>
         <v>11.5</v>
       </c>
@@ -32231,19 +32416,19 @@
         <v>11.5</v>
       </c>
       <c r="P8" s="1"/>
-      <c r="S8" s="46">
+      <c r="S8" s="43">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T8" s="46">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="U8" s="46">
+      <c r="T8" s="43">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="U8" s="43">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="V8" s="46">
+      <c r="V8" s="43">
         <f t="shared" si="3"/>
         <v>11.5</v>
       </c>
@@ -32288,19 +32473,19 @@
         <v>0</v>
       </c>
       <c r="P9" s="1"/>
-      <c r="S9" s="46">
+      <c r="S9" s="43">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="T9" s="46">
+      <c r="T9" s="43">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U9" s="46">
+      <c r="U9" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V9" s="46">
+      <c r="V9" s="43">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
@@ -32345,19 +32530,19 @@
         <v>17.5</v>
       </c>
       <c r="P10" s="1"/>
-      <c r="S10" s="46">
+      <c r="S10" s="43">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T10" s="46">
+      <c r="T10" s="43">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="U10" s="46">
+      <c r="U10" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V10" s="46">
+      <c r="V10" s="43">
         <f t="shared" si="3"/>
         <v>17.5</v>
       </c>
@@ -32402,19 +32587,19 @@
         <v>15.5</v>
       </c>
       <c r="P11" s="1"/>
-      <c r="S11" s="46">
+      <c r="S11" s="43">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T11" s="46">
+      <c r="T11" s="43">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="U11" s="46">
+      <c r="U11" s="43">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="V11" s="46">
+      <c r="V11" s="43">
         <f t="shared" si="3"/>
         <v>15.5</v>
       </c>
@@ -32459,19 +32644,19 @@
         <v>0</v>
       </c>
       <c r="P12" s="1"/>
-      <c r="S12" s="46">
+      <c r="S12" s="43">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="T12" s="46">
+      <c r="T12" s="43">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U12" s="46">
+      <c r="U12" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V12" s="46">
+      <c r="V12" s="43">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
@@ -32516,19 +32701,19 @@
         <v>10.5</v>
       </c>
       <c r="P13" s="1"/>
-      <c r="S13" s="46">
+      <c r="S13" s="43">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="T13" s="46">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="U13" s="46">
+      <c r="T13" s="43">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="U13" s="43">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="V13" s="46">
+      <c r="V13" s="43">
         <f t="shared" si="3"/>
         <v>10.5</v>
       </c>
@@ -32573,19 +32758,19 @@
         <v>18.5</v>
       </c>
       <c r="P14" s="1"/>
-      <c r="S14" s="46">
+      <c r="S14" s="43">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T14" s="46">
+      <c r="T14" s="43">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U14" s="46">
+      <c r="U14" s="43">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="V14" s="46">
+      <c r="V14" s="43">
         <f t="shared" si="3"/>
         <v>18.5</v>
       </c>
@@ -32630,19 +32815,19 @@
         <v>0</v>
       </c>
       <c r="P15" s="1"/>
-      <c r="S15" s="46">
+      <c r="S15" s="43">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="T15" s="46">
+      <c r="T15" s="43">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U15" s="46">
+      <c r="U15" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V15" s="46">
+      <c r="V15" s="43">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
@@ -32687,19 +32872,19 @@
         <v>10.5</v>
       </c>
       <c r="P16" s="1"/>
-      <c r="S16" s="46">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="T16" s="46">
+      <c r="S16" s="43">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="T16" s="43">
         <f t="shared" si="1"/>
         <v>4.5</v>
       </c>
-      <c r="U16" s="46">
+      <c r="U16" s="43">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="V16" s="46">
+      <c r="V16" s="43">
         <f t="shared" si="3"/>
         <v>10.5</v>
       </c>
@@ -32744,19 +32929,19 @@
         <v>15</v>
       </c>
       <c r="P17" s="1"/>
-      <c r="S17" s="46">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="T17" s="46">
+      <c r="S17" s="43">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="T17" s="43">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="U17" s="46">
+      <c r="U17" s="43">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="V17" s="46">
+      <c r="V17" s="43">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
@@ -32801,19 +32986,19 @@
         <v>17.5</v>
       </c>
       <c r="P18" s="1"/>
-      <c r="S18" s="46">
+      <c r="S18" s="43">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="T18" s="46">
+      <c r="T18" s="43">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="U18" s="46">
+      <c r="U18" s="43">
         <f t="shared" si="2"/>
         <v>7.5</v>
       </c>
-      <c r="V18" s="46">
+      <c r="V18" s="43">
         <f t="shared" si="3"/>
         <v>17.5</v>
       </c>
@@ -32858,19 +33043,19 @@
         <v>14</v>
       </c>
       <c r="P19" s="1"/>
-      <c r="S19" s="46">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="T19" s="46">
+      <c r="S19" s="43">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="T19" s="43">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="U19" s="46">
+      <c r="U19" s="43">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="V19" s="46">
+      <c r="V19" s="43">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
@@ -32915,19 +33100,19 @@
         <v>14.5</v>
       </c>
       <c r="P20" s="1"/>
-      <c r="S20" s="46">
+      <c r="S20" s="43">
         <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
-      <c r="T20" s="46">
+      <c r="T20" s="43">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="U20" s="46">
+      <c r="U20" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V20" s="46">
+      <c r="V20" s="43">
         <f t="shared" si="3"/>
         <v>14.5</v>
       </c>
@@ -32972,19 +33157,19 @@
         <v>6</v>
       </c>
       <c r="P21" s="1"/>
-      <c r="S21" s="46">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="T21" s="46">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U21" s="46">
+      <c r="S21" s="43">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="T21" s="43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="43">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="V21" s="46">
+      <c r="V21" s="43">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
@@ -33029,19 +33214,19 @@
         <v>0</v>
       </c>
       <c r="P22" s="1"/>
-      <c r="S22" s="46">
+      <c r="S22" s="43">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="T22" s="46">
+      <c r="T22" s="43">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U22" s="46">
+      <c r="U22" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V22" s="46">
+      <c r="V22" s="43">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
@@ -33086,19 +33271,19 @@
         <v>18</v>
       </c>
       <c r="P23" s="1"/>
-      <c r="S23" s="46">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="T23" s="46">
+      <c r="S23" s="43">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="T23" s="43">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="U23" s="46">
+      <c r="U23" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V23" s="46">
+      <c r="V23" s="43">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
@@ -33143,19 +33328,19 @@
         <v>13</v>
       </c>
       <c r="P24" s="1"/>
-      <c r="S24" s="46">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="T24" s="46">
+      <c r="S24" s="43">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="T24" s="43">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U24" s="46">
+      <c r="U24" s="43">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="V24" s="46">
+      <c r="V24" s="43">
         <f t="shared" si="3"/>
         <v>13</v>
       </c>
@@ -33200,19 +33385,19 @@
         <v>12.5</v>
       </c>
       <c r="P25" s="1"/>
-      <c r="S25" s="46">
+      <c r="S25" s="43">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T25" s="46">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="U25" s="46">
+      <c r="T25" s="43">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="U25" s="43">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="V25" s="46">
+      <c r="V25" s="43">
         <f t="shared" si="3"/>
         <v>12.5</v>
       </c>
@@ -33257,19 +33442,19 @@
         <v>19.5</v>
       </c>
       <c r="P26" s="1"/>
-      <c r="S26" s="46">
+      <c r="S26" s="43">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T26" s="46">
+      <c r="T26" s="43">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U26" s="46">
+      <c r="U26" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V26" s="46">
+      <c r="V26" s="43">
         <f t="shared" si="3"/>
         <v>19.5</v>
       </c>
@@ -33314,19 +33499,19 @@
         <v>19.5</v>
       </c>
       <c r="P27" s="1"/>
-      <c r="S27" s="46">
+      <c r="S27" s="43">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T27" s="46">
+      <c r="T27" s="43">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U27" s="46">
+      <c r="U27" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V27" s="46">
+      <c r="V27" s="43">
         <f t="shared" si="3"/>
         <v>19.5</v>
       </c>
@@ -33371,19 +33556,19 @@
         <v>6</v>
       </c>
       <c r="P28" s="1"/>
-      <c r="S28" s="46">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="T28" s="46">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="U28" s="46">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="V28" s="46">
+      <c r="S28" s="43">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="T28" s="43">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="U28" s="43">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="V28" s="43">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
@@ -33428,19 +33613,19 @@
         <v>0</v>
       </c>
       <c r="P29" s="1"/>
-      <c r="S29" s="46">
+      <c r="S29" s="43">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="T29" s="46">
+      <c r="T29" s="43">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U29" s="46">
+      <c r="U29" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V29" s="46">
+      <c r="V29" s="43">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
@@ -33485,19 +33670,19 @@
         <v>12</v>
       </c>
       <c r="P30" s="1"/>
-      <c r="S30" s="46">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="T30" s="46">
+      <c r="S30" s="43">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="T30" s="43">
         <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="U30" s="46">
+      <c r="U30" s="43">
         <f t="shared" si="2"/>
         <v>7.5</v>
       </c>
-      <c r="V30" s="46">
+      <c r="V30" s="43">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
@@ -33542,19 +33727,19 @@
         <v>11</v>
       </c>
       <c r="P31" s="1"/>
-      <c r="S31" s="46">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="T31" s="46">
+      <c r="S31" s="43">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="T31" s="43">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U31" s="46">
+      <c r="U31" s="43">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="V31" s="46">
+      <c r="V31" s="43">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
@@ -33599,19 +33784,19 @@
         <v>18</v>
       </c>
       <c r="P32" s="1"/>
-      <c r="S32" s="46">
+      <c r="S32" s="43">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="T32" s="46">
+      <c r="T32" s="43">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="U32" s="46">
+      <c r="U32" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V32" s="46">
+      <c r="V32" s="43">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
@@ -33656,19 +33841,19 @@
         <v>15.5</v>
       </c>
       <c r="P33" s="1"/>
-      <c r="S33" s="46">
+      <c r="S33" s="43">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T33" s="46">
+      <c r="T33" s="43">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U33" s="46">
+      <c r="U33" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V33" s="46">
+      <c r="V33" s="43">
         <f t="shared" si="3"/>
         <v>15.5</v>
       </c>
@@ -33713,19 +33898,19 @@
         <v>17.5</v>
       </c>
       <c r="P34" s="1"/>
-      <c r="S34" s="46">
+      <c r="S34" s="43">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="T34" s="46">
+      <c r="T34" s="43">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U34" s="46">
+      <c r="U34" s="43">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="V34" s="46">
+      <c r="V34" s="43">
         <f t="shared" si="3"/>
         <v>17.5</v>
       </c>
@@ -33770,19 +33955,19 @@
         <v>14</v>
       </c>
       <c r="P35" s="1"/>
-      <c r="S35" s="46">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="T35" s="46">
+      <c r="S35" s="43">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="T35" s="43">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U35" s="46">
+      <c r="U35" s="43">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="V35" s="46">
+      <c r="V35" s="43">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
@@ -33827,19 +34012,19 @@
         <v>19</v>
       </c>
       <c r="P36" s="1"/>
-      <c r="S36" s="46">
+      <c r="S36" s="43">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="T36" s="46">
+      <c r="T36" s="43">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="U36" s="46">
+      <c r="U36" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V36" s="46">
+      <c r="V36" s="43">
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
@@ -33884,19 +34069,19 @@
         <v>18.5</v>
       </c>
       <c r="P37" s="1"/>
-      <c r="S37" s="46">
+      <c r="S37" s="43">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T37" s="46">
+      <c r="T37" s="43">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U37" s="46">
+      <c r="U37" s="43">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="V37" s="46">
+      <c r="V37" s="43">
         <f t="shared" si="3"/>
         <v>18.5</v>
       </c>
@@ -33941,19 +34126,19 @@
         <v>18</v>
       </c>
       <c r="P38" s="1"/>
-      <c r="S38" s="46">
+      <c r="S38" s="43">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="T38" s="46">
+      <c r="T38" s="43">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="U38" s="46">
+      <c r="U38" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V38" s="46">
+      <c r="V38" s="43">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
@@ -33998,19 +34183,19 @@
         <v>11.5</v>
       </c>
       <c r="P39" s="1"/>
-      <c r="S39" s="46">
+      <c r="S39" s="43">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="T39" s="46">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="U39" s="46">
+      <c r="T39" s="43">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="U39" s="43">
         <f t="shared" si="2"/>
         <v>5.5</v>
       </c>
-      <c r="V39" s="46">
+      <c r="V39" s="43">
         <f t="shared" si="3"/>
         <v>11.5</v>
       </c>
@@ -34055,19 +34240,19 @@
         <v>13.5</v>
       </c>
       <c r="P40" s="1"/>
-      <c r="S40" s="46">
+      <c r="S40" s="43">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T40" s="46">
+      <c r="T40" s="43">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U40" s="46">
+      <c r="U40" s="43">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="V40" s="46">
+      <c r="V40" s="43">
         <f t="shared" si="3"/>
         <v>13.5</v>
       </c>
@@ -34112,19 +34297,19 @@
         <v>6.5</v>
       </c>
       <c r="P41" s="1"/>
-      <c r="S41" s="46">
+      <c r="S41" s="43">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="T41" s="46">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="U41" s="46">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="V41" s="46">
+      <c r="T41" s="43">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="U41" s="43">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="V41" s="43">
         <f t="shared" si="3"/>
         <v>6.5</v>
       </c>
@@ -34169,19 +34354,19 @@
         <v>0</v>
       </c>
       <c r="P42" s="1"/>
-      <c r="S42" s="46">
+      <c r="S42" s="43">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="T42" s="46">
+      <c r="T42" s="43">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U42" s="46">
+      <c r="U42" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V42" s="46">
+      <c r="V42" s="43">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
@@ -34226,19 +34411,19 @@
         <v>3</v>
       </c>
       <c r="P43" s="1"/>
-      <c r="S43" s="46">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="T43" s="46">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U43" s="46">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="V43" s="46">
+      <c r="S43" s="43">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="T43" s="43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U43" s="43">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="V43" s="43">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
@@ -34283,19 +34468,19 @@
         <v>0</v>
       </c>
       <c r="P44" s="1"/>
-      <c r="S44" s="46">
+      <c r="S44" s="43">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="T44" s="46">
+      <c r="T44" s="43">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U44" s="46">
+      <c r="U44" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V44" s="46">
+      <c r="V44" s="43">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
@@ -34340,19 +34525,19 @@
         <v>14.5</v>
       </c>
       <c r="P45" s="1"/>
-      <c r="S45" s="46">
+      <c r="S45" s="43">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="T45" s="46">
+      <c r="T45" s="43">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U45" s="46">
+      <c r="U45" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V45" s="46">
+      <c r="V45" s="43">
         <f t="shared" si="3"/>
         <v>14.5</v>
       </c>
@@ -34397,19 +34582,19 @@
         <v>4</v>
       </c>
       <c r="P46" s="1"/>
-      <c r="S46" s="46">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="T46" s="46">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="U46" s="46">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V46" s="46">
+      <c r="S46" s="43">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="T46" s="43">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="U46" s="43">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V46" s="43">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
@@ -34454,19 +34639,19 @@
         <v>14.5</v>
       </c>
       <c r="P47" s="1"/>
-      <c r="S47" s="46">
+      <c r="S47" s="43">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T47" s="46">
+      <c r="T47" s="43">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U47" s="46">
+      <c r="U47" s="43">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="V47" s="46">
+      <c r="V47" s="43">
         <f t="shared" si="3"/>
         <v>14.5</v>
       </c>
@@ -34511,19 +34696,19 @@
         <v>7</v>
       </c>
       <c r="P48" s="1"/>
-      <c r="S48" s="46">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="T48" s="46">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="U48" s="46">
+      <c r="S48" s="43">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="T48" s="43">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="U48" s="43">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="V48" s="46">
+      <c r="V48" s="43">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -34568,19 +34753,19 @@
         <v>14.5</v>
       </c>
       <c r="P49" s="1"/>
-      <c r="S49" s="46">
+      <c r="S49" s="43">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T49" s="46">
+      <c r="T49" s="43">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U49" s="46">
+      <c r="U49" s="43">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="V49" s="46">
+      <c r="V49" s="43">
         <f t="shared" si="3"/>
         <v>14.5</v>
       </c>
@@ -34625,19 +34810,19 @@
         <v>0</v>
       </c>
       <c r="P50" s="1"/>
-      <c r="S50" s="46">
+      <c r="S50" s="43">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="T50" s="46">
+      <c r="T50" s="43">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U50" s="46">
+      <c r="U50" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V50" s="46">
+      <c r="V50" s="43">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
@@ -34682,19 +34867,19 @@
         <v>19.5</v>
       </c>
       <c r="P51" s="1"/>
-      <c r="S51" s="46">
+      <c r="S51" s="43">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T51" s="46">
+      <c r="T51" s="43">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U51" s="46">
+      <c r="U51" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V51" s="46">
+      <c r="V51" s="43">
         <f t="shared" si="3"/>
         <v>19.5</v>
       </c>
@@ -34739,19 +34924,19 @@
         <v>17</v>
       </c>
       <c r="P52" s="1"/>
-      <c r="S52" s="46">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="T52" s="46">
+      <c r="S52" s="43">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="T52" s="43">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="U52" s="46">
+      <c r="U52" s="43">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="V52" s="46">
+      <c r="V52" s="43">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
@@ -34796,19 +34981,19 @@
         <v>0</v>
       </c>
       <c r="P53" s="1"/>
-      <c r="S53" s="46">
+      <c r="S53" s="43">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="T53" s="46">
+      <c r="T53" s="43">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U53" s="46">
+      <c r="U53" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V53" s="46">
+      <c r="V53" s="43">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
@@ -34853,19 +35038,19 @@
         <v>18</v>
       </c>
       <c r="P54" s="1"/>
-      <c r="S54" s="46">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="T54" s="46">
+      <c r="S54" s="43">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="T54" s="43">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="U54" s="46">
+      <c r="U54" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V54" s="46">
+      <c r="V54" s="43">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
@@ -34910,19 +35095,19 @@
         <v>19.5</v>
       </c>
       <c r="P55" s="1"/>
-      <c r="S55" s="46">
+      <c r="S55" s="43">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T55" s="46">
+      <c r="T55" s="43">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U55" s="46">
+      <c r="U55" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V55" s="46">
+      <c r="V55" s="43">
         <f t="shared" si="3"/>
         <v>19.5</v>
       </c>
@@ -34967,19 +35152,19 @@
         <v>13</v>
       </c>
       <c r="P56" s="1"/>
-      <c r="S56" s="46">
+      <c r="S56" s="43">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="T56" s="46">
+      <c r="T56" s="43">
         <f t="shared" si="1"/>
         <v>3.5</v>
       </c>
-      <c r="U56" s="46">
+      <c r="U56" s="43">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="V56" s="46">
+      <c r="V56" s="43">
         <f t="shared" si="3"/>
         <v>13</v>
       </c>
@@ -35024,19 +35209,19 @@
         <v>0</v>
       </c>
       <c r="P57" s="1"/>
-      <c r="S57" s="46">
+      <c r="S57" s="43">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="T57" s="46">
+      <c r="T57" s="43">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U57" s="46">
+      <c r="U57" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V57" s="46">
+      <c r="V57" s="43">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
@@ -35081,19 +35266,19 @@
         <v>0</v>
       </c>
       <c r="P58" s="1"/>
-      <c r="S58" s="46">
+      <c r="S58" s="43">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="T58" s="46">
+      <c r="T58" s="43">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="U58" s="46">
+      <c r="U58" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V58" s="46">
+      <c r="V58" s="43">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
@@ -35138,19 +35323,19 @@
         <v>14.5</v>
       </c>
       <c r="P59" s="1"/>
-      <c r="S59" s="46">
+      <c r="S59" s="43">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T59" s="46">
+      <c r="T59" s="43">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U59" s="46">
+      <c r="U59" s="43">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="V59" s="46">
+      <c r="V59" s="43">
         <f t="shared" si="3"/>
         <v>14.5</v>
       </c>
@@ -35195,19 +35380,19 @@
         <v>14.5</v>
       </c>
       <c r="P60" s="1"/>
-      <c r="S60" s="46">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="T60" s="46">
+      <c r="S60" s="43">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="T60" s="43">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U60" s="46">
+      <c r="U60" s="43">
         <f t="shared" si="2"/>
         <v>7.5</v>
       </c>
-      <c r="V60" s="46">
+      <c r="V60" s="43">
         <f t="shared" si="3"/>
         <v>14.5</v>
       </c>
@@ -35252,19 +35437,19 @@
         <v>15.5</v>
       </c>
       <c r="P61" s="1"/>
-      <c r="S61" s="46">
+      <c r="S61" s="43">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T61" s="46">
+      <c r="T61" s="43">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="U61" s="46">
+      <c r="U61" s="43">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="V61" s="46">
+      <c r="V61" s="43">
         <f t="shared" si="3"/>
         <v>15.5</v>
       </c>
@@ -35309,19 +35494,19 @@
         <v>15.5</v>
       </c>
       <c r="P62" s="1"/>
-      <c r="S62" s="46">
+      <c r="S62" s="43">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T62" s="46">
+      <c r="T62" s="43">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U62" s="46">
+      <c r="U62" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V62" s="46">
+      <c r="V62" s="43">
         <f t="shared" si="3"/>
         <v>15.5</v>
       </c>
@@ -35366,19 +35551,19 @@
         <v>17.5</v>
       </c>
       <c r="P63" s="1"/>
-      <c r="S63" s="46">
+      <c r="S63" s="43">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="T63" s="46">
+      <c r="T63" s="43">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="U63" s="46">
+      <c r="U63" s="43">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="V63" s="46">
+      <c r="V63" s="43">
         <f t="shared" si="3"/>
         <v>17.5</v>
       </c>
@@ -35423,19 +35608,19 @@
         <v>15</v>
       </c>
       <c r="P64" s="1"/>
-      <c r="S64" s="46">
+      <c r="S64" s="43">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="T64" s="46">
+      <c r="T64" s="43">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="U64" s="46">
+      <c r="U64" s="43">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="V64" s="46">
+      <c r="V64" s="43">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
@@ -35457,19 +35642,19 @@
       <c r="N65" s="1"/>
       <c r="O65" s="1"/>
       <c r="P65" s="1"/>
-      <c r="S65" s="46">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T65" s="46">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U65" s="46">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V65" s="46">
+      <c r="S65" s="43">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T65" s="43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U65" s="43">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V65" s="43">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
